--- a/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A42CB6E-25FD-4E42-A2B4-92F083274CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F4D7D-CCF7-49C1-A991-F149776908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="840" windowWidth="35745" windowHeight="18900" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
+    <workbookView xWindow="2655" yWindow="2700" windowWidth="35745" windowHeight="18900" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Input - Planting" sheetId="4" r:id="rId1"/>
@@ -178,11 +178,13 @@
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">#REF!</definedName>
     <definedName name="X_Cell_Planting_Latitude">'Input - Planting'!$C$3</definedName>
     <definedName name="X_Cell_Planting_Longitude">'Input - Planting'!$C$4</definedName>
+    <definedName name="X_Cell_Planting_PlantingAreaInHectares">'Input - Planting'!$C$8</definedName>
     <definedName name="X_Cell_Planting_PlantingDate">'Input - Planting'!$C$5</definedName>
     <definedName name="X_Cell_Planting_PlantingName">'Input - Planting'!$C$6</definedName>
     <definedName name="X_Cell_Site_EndDate">'Input - Planting'!$C$12</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Planting'!$C$11</definedName>
     <definedName name="X_Result_Planting_CarbonCapturedPerHectare">'Input - Planting'!$C$15</definedName>
+    <definedName name="X_Result_Planting_CarbonCapturedTotalArea">'Input - Planting'!$C$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -6709,30 +6711,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -6927,26 +6909,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
@@ -6954,7 +6937,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C6F40-9188-4CB0-AF00-56A1D1AE2E37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6971,4 +6954,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F4D7D-CCF7-49C1-A991-F149776908A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CDEAAA-B4CF-43A5-94FA-40DA2CCEF997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2655" yWindow="2700" windowWidth="35745" windowHeight="18900" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="36255" windowHeight="19140" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Input - Planting" sheetId="4" r:id="rId1"/>
@@ -174,8 +174,6 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">#REF!</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">#REF!</definedName>
     <definedName name="X_Cell_Planting_Latitude">'Input - Planting'!$C$3</definedName>
     <definedName name="X_Cell_Planting_Longitude">'Input - Planting'!$C$4</definedName>
     <definedName name="X_Cell_Planting_PlantingAreaInHectares">'Input - Planting'!$C$8</definedName>
@@ -6711,7 +6709,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6910,12 +6913,7 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6930,9 +6928,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6957,9 +6955,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
@@ -8,64 +8,101 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CDEAAA-B4CF-43A5-94FA-40DA2CCEF997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF9CF4-1266-4B58-A17D-7CDBCDF977B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="36255" windowHeight="19140" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
+    <workbookView xWindow="1500" yWindow="810" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Input - Planting" sheetId="4" r:id="rId1"/>
-    <sheet name="Constants - Common" sheetId="6" r:id="rId2"/>
+    <sheet name="Input - Data quality" sheetId="7" r:id="rId2"/>
+    <sheet name="Constants - Common" sheetId="6" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="1">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{CH4} \times GWP_{CH4}")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Title">_xlfn.LAMBDA("Convert methane emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Variable">_xlfn.LAMBDA("ECH4 CO2e")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="1">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{N2O} \times GWP_{N2O}")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="1">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="1">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="1">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="1">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="1">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="1">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="1">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="1">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="1">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="1">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title">_xlfn.LAMBDA("Australian states and territories")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Title">_xlfn.LAMBDA("VEERG Australian climate zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title">_xlfn.LAMBDA("Factor to convert elemental mass of gas to molecular mass")</definedName>
@@ -76,6 +113,7 @@
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Title">_xlfn.LAMBDA("Factor to convert elemental mass of N2O to molecular mass")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Variable">_xlfn.LAMBDA("CgN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Source">_xlfn.LAMBDA("VEERG 2026: XXXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Title">_xlfn.LAMBDA("Australian data scores for scope 3")</definedName>
@@ -86,18 +124,22 @@
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Title">_xlfn.LAMBDA("p = density of methane")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Unit">_xlfn.LAMBDA("kg/m3")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Equation 3.D.B_10")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
@@ -105,81 +147,133 @@
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Source">_xlfn.LAMBDA("VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Title">_xlfn.LAMBDA("VEERG Australian rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Title">_xlfn.LAMBDA("VEERG Australian temperature zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Source">_xlfn.LAMBDA("Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Title">_xlfn.LAMBDA("ABS Statistcal Areas Level 4 - Western Australia")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Title">_xlfn.LAMBDA("VEERG Australian wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain(_xlpm.LivestockClass, _xlpm.MovementDate) * CommonLivestock_InputFunctions.LivestockMovement_DaysMovementToMonthEnd(_xlpm.MovementDate), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, EOMONTH(_xlpm.Month, -1) + 1))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month,_xlpm.HeadAtStartOfMonth, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStartOfMonth) * [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead(_xlpm.LivestockClass, _xlpm.Month))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMovementDateTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.Head, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate) * _xlpm.Head)</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * [0]!CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
+    <definedName name="getOverlappingReportingCycles" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="Result_CarbonRemovalsFromPlantings">[2]Results!$E$50</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1">[2]Results!$E$39</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2">[2]Results!$F$39</definedName>
+    <definedName name="Result_Enterprise_Method1">[2]Results!$H$25</definedName>
+    <definedName name="Result_Enterprise_Method2">[2]Results!$I$25</definedName>
+    <definedName name="Result_NetEmissions_Method1">[2]Results!$E$56</definedName>
+    <definedName name="Result_NetEmissions_Method2">[2]Results!$F$56</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[2]Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'[2]Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'[2]Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Planting_Latitude">'Input - Planting'!$C$3</definedName>
     <definedName name="X_Cell_Planting_Longitude">'Input - Planting'!$C$4</definedName>
     <definedName name="X_Cell_Planting_PlantingAreaInHectares">'Input - Planting'!$C$8</definedName>
     <definedName name="X_Cell_Planting_PlantingDate">'Input - Planting'!$C$5</definedName>
     <definedName name="X_Cell_Planting_PlantingName">'Input - Planting'!$C$6</definedName>
     <definedName name="X_Cell_Site_EndDate">'Input - Planting'!$C$12</definedName>
+    <definedName name="X_Cell_Site_StartDate" localSheetId="1">'[2]Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Planting'!$C$11</definedName>
     <definedName name="X_Result_Planting_CarbonCapturedPerHectare">'Input - Planting'!$C$15</definedName>
     <definedName name="X_Result_Planting_CarbonCapturedTotalArea">'Input - Planting'!$C$16</definedName>
@@ -253,7 +347,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>My cool thing</t>
   </si>
@@ -490,6 +584,42 @@
   </si>
   <si>
     <t>EFNi &amp; EFN2Oi</t>
+  </si>
+  <si>
+    <t>Input - Data quality</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Temporal representativeness</t>
+  </si>
+  <si>
+    <t>Spatial resolution</t>
+  </si>
+  <si>
+    <t>Sample size</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Evidence files</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Input name</t>
+  </si>
+  <si>
+    <t>TR4</t>
+  </si>
+  <si>
+    <t>SR5</t>
+  </si>
+  <si>
+    <t>SS3</t>
   </si>
 </sst>
 </file>
@@ -500,7 +630,7 @@
     <numFmt numFmtId="164" formatCode="[$-C09]dd\-mmmm\-yyyy;@"/>
     <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -606,8 +736,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFCC6600"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF533001"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,6 +769,28 @@
         <fgColor rgb="FF183C1B"/>
         <bgColor indexed="64"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF533001"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="1">
+          <color theme="0" tint="-5.0965910824915313E-2"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
   <borders count="2">
@@ -651,7 +817,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -685,8 +851,25 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -740,15 +923,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="13"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="15">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="16" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="17">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="13">
+  <cellStyles count="19">
     <cellStyle name="Block heading" xfId="9" xr:uid="{6065A2C3-09F5-4515-87ED-A07ECE03B60A}"/>
     <cellStyle name="Content bold" xfId="1" xr:uid="{90EECC7A-90CF-4913-9525-0D57B2C3C25A}"/>
     <cellStyle name="Content normal" xfId="8" xr:uid="{7064D260-35DF-4E40-B005-5927849D5F2D}"/>
     <cellStyle name="Equation source" xfId="10" xr:uid="{A6980CD5-F033-4A4E-A310-20CA2DBA147C}"/>
     <cellStyle name="Information variation" xfId="11" xr:uid="{3DFDDBB8-017E-4A9E-BD36-920C2DA5EB07}"/>
     <cellStyle name="Input date" xfId="2" xr:uid="{2CBAF3EB-BBB3-44B0-B98B-27C0B711C4C8}"/>
+    <cellStyle name="Input number general calculated" xfId="18" xr:uid="{17116EAE-73FE-4584-B1D1-DA7A2E1BE7F3}"/>
     <cellStyle name="Input number no decimals calculated" xfId="3" xr:uid="{3E2DE6DD-181A-4A3F-B39E-0927DF0A1DA2}"/>
+    <cellStyle name="Input page heading" xfId="13" xr:uid="{1040356A-2362-4675-A6C2-D285FDE9B237}"/>
+    <cellStyle name="Input page section heading" xfId="14" xr:uid="{B0C6AFFF-01F0-417A-921C-B83B5F6523C6}"/>
+    <cellStyle name="Input select" xfId="17" xr:uid="{5330A20B-6680-4771-B4C8-C6ABDA2A591E}"/>
+    <cellStyle name="Input table column header" xfId="15" xr:uid="{9C39E355-B94C-4E3D-B2C2-ACCB276438BC}"/>
+    <cellStyle name="Input text" xfId="16" xr:uid="{5F26ED4A-B6DD-42BD-95D5-C01AC860788C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="6" xr:uid="{EE6542E1-CDF9-4701-B44A-AABE5F401092}"/>
     <cellStyle name="Page heading" xfId="4" xr:uid="{5606267B-8272-44F0-B060-3CC8D7791322}"/>
@@ -756,7 +962,104 @@
     <cellStyle name="Page source" xfId="5" xr:uid="{BDB1E337-77B0-445D-A39B-72CE8D02F2A9}"/>
     <cellStyle name="Unit no indent" xfId="12" xr:uid="{1E2A3F46-D52F-45EA-B250-19AA59D3DC20}"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="48">
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF533001"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFCC66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1724,14 +2027,22 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{BB0715A8-E541-48D6-9C7A-67E469073C29}">
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="totalRow" dxfId="3"/>
+      <tableStyleElement type="firstColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{F81B4736-567E-441A-AD84-F5C27A32236A}">
-      <tableStyleElement type="wholeTable" dxfId="41"/>
-      <tableStyleElement type="headerRow" dxfId="40"/>
-      <tableStyleElement type="totalRow" dxfId="39"/>
-      <tableStyleElement type="firstColumn" dxfId="38"/>
-      <tableStyleElement type="firstRowStripe" dxfId="37"/>
-      <tableStyleElement type="secondRowStripe" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="totalRow" dxfId="45"/>
+      <tableStyleElement type="firstColumn" dxfId="44"/>
+      <tableStyleElement type="firstRowStripe" dxfId="43"/>
+      <tableStyleElement type="secondRowStripe" dxfId="42"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1743,6 +2054,108 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Input - Data quality"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Results"/>
+      <sheetName val="Input - Site"/>
+      <sheetName val="Input - Enterprise"/>
+      <sheetName val="Input - Fert Prod System"/>
+      <sheetName val="Input - Data quality"/>
+      <sheetName val="Constants - Common"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="25">
+          <cell r="H25" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="I25" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="E39" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F39" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="E50">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="E56" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F56" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="12">
+          <cell r="E12">
+            <v>45658</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>45962</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>46112</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32">
+            <v>0.8</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1810,28 +2223,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ECEAE884-E3AA-4C6F-B76F-5EC80216329E}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
-  <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{6C4E1D2F-185E-4B56-9A04-9422B9FAEAAE}" name="Table_Input_DataQuality" displayName="Table_Input_DataQuality" ref="D6:J7" totalsRowShown="0" headerRowCellStyle="Input table column header">
+  <autoFilter ref="D6:J7" xr:uid="{13023411-FAD9-40B6-9366-7826422CBF8A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7FC2ED6E-9CC3-451B-BB51-1CF60EA95BE7}" name="State/Territory">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9A5B16F9-8C3A-4E71-8E75-E40E63477857}" name="Input"/>
+    <tableColumn id="2" xr3:uid="{B36C3A6D-5D2A-411F-8FDF-551B0F91C2B2}" name="Temporal representativeness" dataCellStyle="Input select"/>
+    <tableColumn id="3" xr3:uid="{A6FBA595-4E78-4D43-B95A-D7307772AFEE}" name="Spatial resolution" dataCellStyle="Input select"/>
+    <tableColumn id="4" xr3:uid="{A2F061E9-0C51-48C7-A233-819FE284ECD7}" name="Sample size" dataCellStyle="Input select"/>
+    <tableColumn id="5" xr3:uid="{2E8B5CE6-9BDF-4858-A2F6-C5AE1E37112E}" name="Notes"/>
+    <tableColumn id="6" xr3:uid="{4EADE9A3-44EC-401C-9228-5E041AD07075}" name="Evidence files"/>
+    <tableColumn id="7" xr3:uid="{B03E4480-1618-4C18-9AFD-9C12B3203028}" name="Score" dataCellStyle="Input number general calculated">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[1]!Table_SourceData_DataQuality_SampleSize[ID],[1]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{69FDD198-8517-445D-B48E-3D2F8192DDD6}" name="Common Name">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+  </tableColumns>
+  <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6BFD8A0E-B27E-43DA-A0E4-918FC747A35D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+  <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8F7E89B4-998D-4DCC-8DB5-EE50FBC9044D}" name="Leaching Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CC167379-513B-4F97-B5CC-453590524E9E}" name="Abbreviation">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{7E282AA3-2A6C-4BC2-9C13-583E49B8159F}" name="Leaching criteria">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{12F8945C-3C7F-437A-87E1-5C474CC552CC}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1849,7 +2284,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{860C9BB3-289E-4BF9-963B-D9E831D692A7}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1859,7 +2294,7 @@
     <tableColumn id="1" xr3:uid="{A4F762A8-F9FE-4D0C-B506-D39355F3E495}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{08DE5D95-83C8-45AD-A4FC-3CBFDBE7F607}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{08DE5D95-83C8-45AD-A4FC-3CBFDBE7F607}" name="FracWET" dataDxfId="25">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1867,7 +2302,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9E823136-6F0B-4559-B2A4-73793AFF37C3}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1897,7 +2332,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{CB9FD9DD-AB9D-419C-B101-1DFD26654714}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1907,7 +2342,7 @@
     <tableColumn id="1" xr3:uid="{D76B8E07-1FA0-4614-BF71-C5ADE4FC4D02}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33A601DF-5E41-4B94-967E-5711C13EF63D}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{33A601DF-5E41-4B94-967E-5711C13EF63D}" name="FracWET" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1915,7 +2350,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{C650C529-FB9D-496B-B75E-3D6D5558113D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1925,7 +2360,7 @@
     <tableColumn id="1" xr3:uid="{84ACFDA4-3026-4858-A46B-0DB6786BAA53}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DB2AE5D7-1B82-415D-B7E3-8CD68118CDA7}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DB2AE5D7-1B82-415D-B7E3-8CD68118CDA7}" name="EFPRP" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1933,7 +2368,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{857B77BB-B850-4F16-B437-1DFD53F55C30}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1943,7 +2378,7 @@
     <tableColumn id="1" xr3:uid="{38AA1117-3BD9-46E8-8AE1-FED06E15DCD7}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0AEA01EE-06E5-4002-B0B9-07CF152E1D88}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0AEA01EE-06E5-4002-B0B9-07CF152E1D88}" name="Season" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1951,7 +2386,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{F5F7AFF8-F888-4630-83A1-BA07EB5F355F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -1975,49 +2410,49 @@
     <tableColumn id="1" xr3:uid="{F83A96DA-8175-4325-80E8-F0902733D255}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CB521F23-7709-409E-8457-124973047788}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CB521F23-7709-409E-8457-124973047788}" name="MAT (ºC)" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C4CFF46D-BCB9-4346-82D8-732B9774B020}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{C4CFF46D-BCB9-4346-82D8-732B9774B020}" name="Anaerobic lagoon" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CC02EB56-DF2A-4DBF-89DB-C60136C41B78}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{CC02EB56-DF2A-4DBF-89DB-C60136C41B78}" name="Digester / covered lagoons" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A7C14051-C9CF-4AD7-B568-62D0DA4C6C88}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{A7C14051-C9CF-4AD7-B568-62D0DA4C6C88}" name="Liquid systems" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9BFB0B87-AF73-4199-A0F4-249625F3E94A}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{9BFB0B87-AF73-4199-A0F4-249625F3E94A}" name="Daily spread" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5B4CC1F9-79F9-4225-A482-8D9F2B38607D}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{5B4CC1F9-79F9-4225-A482-8D9F2B38607D}" name="Composting (passive windrow)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C67915E4-55C4-4DFE-AC34-7FEF63096ABF}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{C67915E4-55C4-4DFE-AC34-7FEF63096ABF}" name="Solid storage" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{56A9FA80-890E-4119-B8C6-80060AFA757D}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{56A9FA80-890E-4119-B8C6-80060AFA757D}" name="Pit storage" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C1E464C9-BB3C-4349-80E5-E040EEFC92D3}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C1E464C9-BB3C-4349-80E5-E040EEFC92D3}" name="Deep litter" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6510F327-7673-48CD-949B-4E2593CC88C7}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{6510F327-7673-48CD-949B-4E2593CC88C7}" name="Poultry manure with bedding" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BED0BB92-704A-4D5B-915E-B535AA23FFE9}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{BED0BB92-704A-4D5B-915E-B535AA23FFE9}" name="Poultry manure without bedding" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{7F6B929D-02BF-42F7-A9BF-ECD48D8B5D37}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{7F6B929D-02BF-42F7-A9BF-ECD48D8B5D37}" name="Direct processing" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{829A2829-745F-4D05-93C4-6FD42C67E6D4}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{829A2829-745F-4D05-93C4-6FD42C67E6D4}" name="Direct application" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{54827D74-DE91-4D54-93AF-24C63D8E5FA6}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{54827D74-DE91-4D54-93AF-24C63D8E5FA6}" name="Pasture range and paddock" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A855CCC3-ABEA-4445-8B01-8ED0F1FCCB98}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{A855CCC3-ABEA-4445-8B01-8ED0F1FCCB98}" name="MAT raw" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2025,7 +2460,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB3A5C90-13B8-4E18-8FA4-BB68BDBCA5BE}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2035,7 +2470,7 @@
     <tableColumn id="1" xr3:uid="{77A1EB56-28D9-467A-AF37-B37086F57087}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF01B99A-E2BB-4F5D-82E2-8C5B51CF74AF}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AF01B99A-E2BB-4F5D-82E2-8C5B51CF74AF}" name="EFNi &amp; EFN2Oi" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2044,6 +2479,28 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ECEAE884-E3AA-4C6F-B76F-5EC80216329E}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+  <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{7FC2ED6E-9CC3-451B-BB51-1CF60EA95BE7}" name="State/Territory">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{69FDD198-8517-445D-B48E-3D2F8192DDD6}" name="Common Name">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{CC167379-513B-4F97-B5CC-453590524E9E}" name="Abbreviation">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8E528ABB-A26F-400A-BD77-8DD10E99203E}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2057,7 +2514,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AF4E352C-0731-4A89-995E-0577E0F81CAC}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2075,7 +2532,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C3E783B8-6109-4CA2-8525-8E3ACAC4A2E2}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2105,7 +2562,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AB0AAAA7-F92F-42F5-85EE-5E3F3264F356}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2129,49 +2586,49 @@
     <tableColumn id="1" xr3:uid="{6B14D34F-47D9-4E7B-8F67-CFF2BA3972F3}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{03D79397-427F-4BDD-85F7-C446814C4630}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{03D79397-427F-4BDD-85F7-C446814C4630}" name="MAT" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{513FFB98-589A-4C52-B02E-C13C07167123}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{513FFB98-589A-4C52-B02E-C13C07167123}" name="MAP" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{851B3A05-D860-4BC9-8FF0-AA7455D1A0B6}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{851B3A05-D860-4BC9-8FF0-AA7455D1A0B6}" name="Frost days per year" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{111DCB69-2E86-452A-B93A-BB116EFF4325}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{111DCB69-2E86-452A-B93A-BB116EFF4325}" name="Elevation" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{EC9B3EBF-3D45-47C7-A0FC-3AAAB728216D}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{EC9B3EBF-3D45-47C7-A0FC-3AAAB728216D}" name="MAP:PET" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DEE780F3-8FFA-489F-8BF5-29BB91E9B886}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{DEE780F3-8FFA-489F-8BF5-29BB91E9B886}" name="Min temp" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B796F2C1-4462-489B-B059-A97C3CB09E44}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B796F2C1-4462-489B-B059-A97C3CB09E44}" name="Max temp" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{77FF4CA7-BCFB-4B5C-BCB0-CB746D9404FB}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{77FF4CA7-BCFB-4B5C-BCB0-CB746D9404FB}" name="Min rainfall" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{70480799-57AD-475D-8EFB-ECBA87036E18}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{70480799-57AD-475D-8EFB-ECBA87036E18}" name="Max rainfall" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F20E603D-FAAB-4E85-8158-CCCAEF0C348A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{F20E603D-FAAB-4E85-8158-CCCAEF0C348A}" name="Min frost days" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1CA64B37-B900-4123-9FA9-9F8F3122E9E6}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{1CA64B37-B900-4123-9FA9-9F8F3122E9E6}" name="Max frost days" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7C463F98-D060-4671-AAED-63888110DC70}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{7C463F98-D060-4671-AAED-63888110DC70}" name="Min elevation" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{DDE870B0-2FB3-449F-A8E3-315A6DD8565C}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{DDE870B0-2FB3-449F-A8E3-315A6DD8565C}" name="Max elevation" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B5E2ADB7-D4D8-4A56-B4DC-C29288E8C038}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{B5E2ADB7-D4D8-4A56-B4DC-C29288E8C038}" name="Min MAP:PET" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{05917C51-1048-4C05-B02E-F19C0EBAB3ED}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{05917C51-1048-4C05-B02E-F19C0EBAB3ED}" name="Max MAP:PET" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2179,7 +2636,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F669204B-D068-44A2-9480-8A66165B3EAE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2189,7 +2646,7 @@
     <tableColumn id="1" xr3:uid="{C09B5C83-2A18-415A-8927-96C97C2B88AA}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EC38C61-E15D-47AA-A64C-8434A7A2E790}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{7EC38C61-E15D-47AA-A64C-8434A7A2E790}" name="Wet or Dry Zone" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2197,7 +2654,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4CFAC30E-767E-441C-9CAB-02CF9F402801}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2223,7 +2680,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4B53211D-6A46-4AAE-B337-B836933DB48C}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -2243,24 +2700,6 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{0051EE80-A4A4-414E-9CC7-9F2ED58BBBD9}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6BFD8A0E-B27E-43DA-A0E4-918FC747A35D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
-  <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8F7E89B4-998D-4DCC-8DB5-EE50FBC9044D}" name="Leaching Zone">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{7E282AA3-2A6C-4BC2-9C13-583E49B8159F}" name="Leaching criteria">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2717,6 +3156,107 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E90AF6D-9069-486F-86F8-B38023044376}">
+  <sheetPr>
+    <tabColor rgb="FFCC6600"/>
+  </sheetPr>
+  <dimension ref="C1:M7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="4.125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="42.875" style="15" customWidth="1"/>
+    <col min="5" max="7" width="26.875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="88.625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="65.25" style="15" customWidth="1"/>
+    <col min="10" max="13" width="26.875" style="15" customWidth="1"/>
+    <col min="14" max="14" width="26.875" style="10" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:13" s="23" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="C1" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="3:13" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D6" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D7" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="28">
+        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[1]!Table_SourceData_DataQuality_SampleSize[ID],[1]!Table_SourceData_DataQuality_SampleSize[Score])</f>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7" xr:uid="{55B06BCC-92EE-40E9-96B5-52BD30A8679E}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_SampleSize[ID]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{31066E02-D9AC-4AF9-AA7B-2A1D321E9C14}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_SpatialRepresentativeness[ID]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7" xr:uid="{D7E1FE23-F157-4ED2-B848-454A8FC55D46}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_TemporalRepresentativeness[ID]")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5D8088-0800-4A2B-8100-637E09B303F8}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -6718,6 +7258,21 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -6912,21 +7467,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
   <ds:schemaRefs>
@@ -6936,6 +7476,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C6F40-9188-4CB0-AF00-56A1D1AE2E37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6952,23 +7511,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_EnvironmentalPlantings_Template_WIP_v01.xlsx
@@ -8,101 +8,100 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF9CF4-1266-4B58-A17D-7CDBCDF977B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BF629E-FC94-44E3-A9C6-BD1207950CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="810" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{7E1466D3-CE15-41E6-A7E5-3351E07F3C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Input - Planting" sheetId="4" r:id="rId1"/>
     <sheet name="Input - Data quality" sheetId="7" r:id="rId2"/>
-    <sheet name="Constants - Common" sheetId="6" r:id="rId3"/>
+    <sheet name="Constants - Common" sheetId="8" r:id="rId3"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="1">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{CH4} \times GWP_{CH4}")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Title">_xlfn.LAMBDA("Convert methane emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Variable">_xlfn.LAMBDA("ECH4 CO2e")</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="1">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{N2O} \times GWP_{N2O}")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="1">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="1">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
-    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
-    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="1">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart,
+    _xlfn.LET(
+        _xlpm.S,_xlpm.ProductionCycleStart,
+        _xlpm.E,_xlpm.ProductionCycleEnd,
+        _xlpm.m,MONTH(_xlpm.ReportingCycleStart),
+        _xlpm.d,DAY(_xlpm.ReportingCycleStart),
+        _xlpm.PeriodEnd,_xlfn.LAMBDA(_xlpm.st,EDATE(_xlpm.st,12)-1),
+        _xlpm.A,_xlpm.S-365,
+        _xlpm.ya,YEAR(_xlpm.A),
+        _xlpm.yb,YEAR(_xlpm.E),
+        _xlpm.firstYear,_xlpm.ya+(_xlpm.PeriodEnd(DATE(_xlpm.ya,_xlpm.m,_xlpm.d))&lt;_xlpm.S),
+        _xlpm.lastYear,_xlpm.yb-(DATE(_xlpm.yb,_xlpm.m,_xlpm.d)&gt;_xlpm.E),
+        _xlpm.n,MAX(0,_xlpm.lastYear-_xlpm.firstYear+1),
+        _xlpm.yrs,_xlfn.SEQUENCE(_xlpm.n,1,_xlpm.firstYear,1),
+        _xlpm.starts,DATE(_xlpm.yrs,_xlpm.m,_xlpm.d),
+        _xlpm.ends,_xlfn.MAP(_xlpm.starts,_xlpm.PeriodEnd),
+        _xlpm.tag,IF(_xlpm.starts=_xlpm.ReportingCycleStart," (This reporting cycle)",""),
+        _xlpm.startsText,TEXT(_xlpm.starts,"dd mmm yyyy"),
+        _xlpm.endsText,TEXT(_xlpm.ends,"dd mmm yyyy"),
+        IF(_xlpm.n=0,"",_xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="1">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="1">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="1">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="1">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="1">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="1">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="1">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="1">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="1">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title">_xlfn.LAMBDA("Australian states and territories")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Title">_xlfn.LAMBDA("VEERG Australian climate zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title">_xlfn.LAMBDA("Factor to convert elemental mass of gas to molecular mass")</definedName>
@@ -113,7 +112,6 @@
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Title">_xlfn.LAMBDA("Factor to convert elemental mass of N2O to molecular mass")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Variable">_xlfn.LAMBDA("CgN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Source">_xlfn.LAMBDA("VEERG 2026: XXXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Title">_xlfn.LAMBDA("Australian data scores for scope 3")</definedName>
@@ -124,22 +122,24 @@
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Title">_xlfn.LAMBDA("p = density of methane")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Unit">_xlfn.LAMBDA("kg/m3")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Equation 3.D.B_10")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(14, 5,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
@@ -147,93 +147,96 @@
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Source">_xlfn.LAMBDA("VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(3, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(21, 16,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Title">_xlfn.LAMBDA("VEERG Australian rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Title">_xlfn.LAMBDA("VEERG Australian temperature zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Source">_xlfn.LAMBDA("Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Title">_xlfn.LAMBDA("ABS Statistcal Areas Level 4 - Western Australia")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Title">_xlfn.LAMBDA("VEERG Australian wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="1">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="2">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="2">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="2">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -245,35 +248,36 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="2">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="2">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
-    <definedName name="getOverlappingReportingCycles" localSheetId="1">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="Result_CarbonRemovalsFromPlantings">[2]Results!$E$50</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method1">[2]Results!$E$39</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method2">[2]Results!$F$39</definedName>
-    <definedName name="Result_Enterprise_Method1">[2]Results!$H$25</definedName>
-    <definedName name="Result_Enterprise_Method2">[2]Results!$I$25</definedName>
-    <definedName name="Result_NetEmissions_Method1">[2]Results!$E$56</definedName>
-    <definedName name="Result_NetEmissions_Method2">[2]Results!$F$56</definedName>
-    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[2]Input - Enterprise'!$E$32</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'[2]Input - Enterprise'!$E$19</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'[2]Input - Enterprise'!$E$18</definedName>
+    <definedName name="Result_CarbonRemovalsFromPlantings">[1]Results!$E$50</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1">[1]Results!$E$39</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2">[1]Results!$F$39</definedName>
+    <definedName name="Result_Enterprise_Method1">[1]Results!$H$25</definedName>
+    <definedName name="Result_Enterprise_Method2">[1]Results!$I$25</definedName>
+    <definedName name="Result_NetEmissions_Method1">[1]Results!$E$56</definedName>
+    <definedName name="Result_NetEmissions_Method2">[1]Results!$F$56</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[1]Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'[1]Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'[1]Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Planting_Latitude">'Input - Planting'!$C$3</definedName>
     <definedName name="X_Cell_Planting_Longitude">'Input - Planting'!$C$4</definedName>
     <definedName name="X_Cell_Planting_PlantingAreaInHectares">'Input - Planting'!$C$8</definedName>
     <definedName name="X_Cell_Planting_PlantingDate">'Input - Planting'!$C$5</definedName>
     <definedName name="X_Cell_Planting_PlantingName">'Input - Planting'!$C$6</definedName>
     <definedName name="X_Cell_Site_EndDate">'Input - Planting'!$C$12</definedName>
-    <definedName name="X_Cell_Site_StartDate" localSheetId="1">'[2]Input - Enterprise'!$E$12</definedName>
+    <definedName name="X_Cell_Site_StartDate" localSheetId="1">'[1]Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Planting'!$C$11</definedName>
     <definedName name="X_Result_Planting_CarbonCapturedPerHectare">'Input - Planting'!$C$15</definedName>
     <definedName name="X_Result_Planting_CarbonCapturedTotalArea">'Input - Planting'!$C$16</definedName>
@@ -347,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="136">
   <si>
     <t>My cool thing</t>
   </si>
@@ -620,6 +624,141 @@
   </si>
   <si>
     <t>SS3</t>
+  </si>
+  <si>
+    <t>APPENDICES</t>
+  </si>
+  <si>
+    <t>Data quality scoring</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_TemporalRepresentativeness</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Data collected covers the time-period for which emissions are being estimated  </t>
+  </si>
+  <si>
+    <t>TR5</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 2 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 3 years of to the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 4 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>Age of data unknown or data more than 4 years older than the time-period being reported  </t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SpatialRepresentativeness</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) with spatial partitioning or using stratified sampling within property </t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) without spatial partitioning within property  </t>
+  </si>
+  <si>
+    <t>SR4</t>
+  </si>
+  <si>
+    <t>Data based on regional data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR3</t>
+  </si>
+  <si>
+    <t>Data based on state data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Data based on national data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SampleSize</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &gt;90% (e.g. total annual fuel purchases) </t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 51-90%  </t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 21-50%  </t>
+  </si>
+  <si>
+    <t>Data based on sample size of &lt;20% (e.g. liveweight measured for 10% of herd) </t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>Unknown (e.g. data based on national/state/regional data source) </t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_Scope3</t>
+  </si>
+  <si>
+    <t>Verified data provided by supplier consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard </t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Unverified supplier data, consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard, or consistent with these Guidelines (where appropriate)</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Regionally relevant product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Nationally relevant product specific value from database developed using international best practice   </t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Geographically generic product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S31</t>
   </si>
 </sst>
 </file>
@@ -630,7 +769,7 @@
     <numFmt numFmtId="164" formatCode="[$-C09]dd\-mmmm\-yyyy;@"/>
     <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -750,8 +889,26 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -792,8 +949,20 @@
         </stop>
       </gradientFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -816,8 +985,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -868,8 +1046,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -940,8 +1127,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="19">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="20" applyFont="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="21">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="22">
     <cellStyle name="Block heading" xfId="9" xr:uid="{6065A2C3-09F5-4515-87ED-A07ECE03B60A}"/>
     <cellStyle name="Content bold" xfId="1" xr:uid="{90EECC7A-90CF-4913-9525-0D57B2C3C25A}"/>
     <cellStyle name="Content normal" xfId="8" xr:uid="{7064D260-35DF-4E40-B005-5927849D5F2D}"/>
@@ -955,6 +1151,9 @@
     <cellStyle name="Input select" xfId="17" xr:uid="{5330A20B-6680-4771-B4C8-C6ABDA2A591E}"/>
     <cellStyle name="Input table column header" xfId="15" xr:uid="{9C39E355-B94C-4E3D-B2C2-ACCB276438BC}"/>
     <cellStyle name="Input text" xfId="16" xr:uid="{5F26ED4A-B6DD-42BD-95D5-C01AC860788C}"/>
+    <cellStyle name="Menu link default" xfId="19" xr:uid="{F18E4333-B96F-4E07-90FB-6EDE21B99D41}"/>
+    <cellStyle name="Menu link selected" xfId="21" xr:uid="{4D086C84-4B2C-49AA-916D-60A51A6710C6}"/>
+    <cellStyle name="Menu section title" xfId="20" xr:uid="{BBD1C251-AE66-410B-B804-15966527D315}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="6" xr:uid="{EE6542E1-CDF9-4701-B44A-AABE5F401092}"/>
     <cellStyle name="Page heading" xfId="4" xr:uid="{5606267B-8272-44F0-B060-3CC8D7791322}"/>
@@ -962,103 +1161,30 @@
     <cellStyle name="Page source" xfId="5" xr:uid="{BDB1E337-77B0-445D-A39B-72CE8D02F2A9}"/>
     <cellStyle name="Unit no indent" xfId="12" xr:uid="{1E2A3F46-D52F-45EA-B250-19AA59D3DC20}"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="49">
     <dxf>
       <font>
-        <color theme="1" tint="0.24994659260841701"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.24994659260841701"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF533001"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFCC66"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.24994659260841701"/>
-      </font>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2026,23 +2152,120 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF533001"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFCC66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.24994659260841701"/>
+      </font>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{BB0715A8-E541-48D6-9C7A-67E469073C29}">
-      <tableStyleElement type="wholeTable" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="totalRow" dxfId="3"/>
-      <tableStyleElement type="firstColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="48"/>
+      <tableStyleElement type="headerRow" dxfId="47"/>
+      <tableStyleElement type="totalRow" dxfId="46"/>
+      <tableStyleElement type="firstColumn" dxfId="45"/>
+      <tableStyleElement type="firstRowStripe" dxfId="44"/>
+      <tableStyleElement type="secondRowStripe" dxfId="43"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{F81B4736-567E-441A-AD84-F5C27A32236A}">
-      <tableStyleElement type="wholeTable" dxfId="47"/>
-      <tableStyleElement type="headerRow" dxfId="46"/>
-      <tableStyleElement type="totalRow" dxfId="45"/>
-      <tableStyleElement type="firstColumn" dxfId="44"/>
-      <tableStyleElement type="firstRowStripe" dxfId="43"/>
-      <tableStyleElement type="secondRowStripe" dxfId="42"/>
+      <tableStyleElement type="wholeTable" dxfId="42"/>
+      <tableStyleElement type="headerRow" dxfId="41"/>
+      <tableStyleElement type="totalRow" dxfId="40"/>
+      <tableStyleElement type="firstColumn" dxfId="39"/>
+      <tableStyleElement type="firstRowStripe" dxfId="38"/>
+      <tableStyleElement type="secondRowStripe" dxfId="37"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2057,29 +2280,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Input - Data quality"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2153,6 +2353,27 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2241,7 +2462,7 @@
     <tableColumn id="5" xr3:uid="{2E8B5CE6-9BDF-4858-A2F6-C5AE1E37112E}" name="Notes"/>
     <tableColumn id="6" xr3:uid="{4EADE9A3-44EC-401C-9228-5E041AD07075}" name="Evidence files"/>
     <tableColumn id="7" xr3:uid="{B03E4480-1618-4C18-9AFD-9C12B3203028}" name="Score" dataCellStyle="Input number general calculated">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[1]!Table_SourceData_DataQuality_SampleSize[ID],[1]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2249,16 +2470,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6BFD8A0E-B27E-43DA-A0E4-918FC747A35D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{E8C75C6C-5A0F-4F18-86D2-07FDA33A7B8F}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8F7E89B4-998D-4DCC-8DB5-EE50FBC9044D}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{4C328FE0-0CC1-4AA8-8657-CCA18A9AB819}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7E282AA3-2A6C-4BC2-9C13-583E49B8159F}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{B4BBC09D-25D5-48C6-8EC8-101E73DD5C62}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2267,16 +2488,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{12F8945C-3C7F-437A-87E1-5C474CC552CC}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{19654206-678F-4FA3-8759-43E5E56FE33A}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E4570706-FF58-499B-9757-DAC9AEA9472D}" name="Data source">
+    <tableColumn id="1" xr3:uid="{BEDEBA4C-5C70-4CA5-B3ED-D58AD25021BB}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C9173D1-10D3-47AC-854D-32275B22BBC9}" name="Data score">
+    <tableColumn id="2" xr3:uid="{759DB2A8-829E-4DCA-B4B8-695E00D419A7}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2285,16 +2506,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{860C9BB3-289E-4BF9-963B-D9E831D692A7}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EAE17E78-ADE5-4F24-85E6-1AFFF21DD51F}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A4F762A8-F9FE-4D0C-B506-D39355F3E495}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{71AC32D5-1F95-44E3-8A60-C83C205D0818}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{08DE5D95-83C8-45AD-A4FC-3CBFDBE7F607}" name="FracWET" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{3A7C4543-4EFE-4C64-AD4E-C77F5BE87759}" name="FracWET" dataDxfId="20">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2303,7 +2524,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9E823136-6F0B-4559-B2A4-73793AFF37C3}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{76608166-ED7B-4FA2-871D-42591D9F82CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2312,19 +2533,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{479DC45A-3E8A-4E6F-9D5A-066EBCA06C9A}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{5A15BAC9-3A79-4F09-A7D6-8521CE1E9BF8}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3227515F-0DDB-4F5E-B078-58944E063222}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{13D7BC03-63FB-4FA8-8275-F1DBB7E79167}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{33D91403-C1B8-4D05-A289-E972F6D24634}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{9355E005-41CB-4244-A426-F8EB6685118F}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{000DD2E9-BE34-4016-A428-5BEDC873739E}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{422AF928-8B9C-45BF-9BBF-F63CF34891ED}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{324279FF-D528-4AF4-A897-6548792A41E1}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{F9EB399F-F634-432D-BA5A-8AA76782DFBE}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2333,16 +2554,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{CB9FD9DD-AB9D-419C-B101-1DFD26654714}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{C64AFF8B-A35D-44E3-BBA4-7453B49075CB}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D76B8E07-1FA0-4614-BF71-C5ADE4FC4D02}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{CC01D62F-1834-40C2-9BB0-EF7883C29AFC}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33A601DF-5E41-4B94-967E-5711C13EF63D}" name="FracWET" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B92BCEE4-C7BC-4A60-9296-D3BA7D319EA3}" name="FracWET" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2351,16 +2572,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{C650C529-FB9D-496B-B75E-3D6D5558113D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{7C831A5D-7F53-410A-B535-C272EB0CBE7A}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{84ACFDA4-3026-4858-A46B-0DB6786BAA53}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{7A61B0B2-01D4-4265-AC07-0C283A45B5F5}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DB2AE5D7-1B82-415D-B7E3-8CD68118CDA7}" name="EFPRP" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{840FBA7D-F946-42E5-8840-79709FC7DADB}" name="EFPRP" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2369,16 +2590,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{857B77BB-B850-4F16-B437-1DFD53F55C30}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{4726EC83-D820-400A-94FF-13B9640357CD}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{38AA1117-3BD9-46E8-8AE1-FED06E15DCD7}" name="Month">
+    <tableColumn id="1" xr3:uid="{3721320A-BD46-462E-AED0-02D5CE592D82}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0AEA01EE-06E5-4002-B0B9-07CF152E1D88}" name="Season" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F7CBC3F4-82AC-4D05-80E8-BFBA082C1C08}" name="Season" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2387,7 +2608,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{F5F7AFF8-F888-4630-83A1-BA07EB5F355F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{290FBD30-3454-4C59-B8ED-87A62E67E23A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2407,52 +2628,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F83A96DA-8175-4325-80E8-F0902733D255}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{9ECFE791-4613-4588-9A30-C29680420CF0}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CB521F23-7709-409E-8457-124973047788}" name="MAT (ºC)" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{86DDCA26-F494-42AB-A341-2DC2A530F7CC}" name="MAT (ºC)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C4CFF46D-BCB9-4346-82D8-732B9774B020}" name="Anaerobic lagoon" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F6110C1E-C462-4548-B0C3-C8EFC0C38A75}" name="Anaerobic lagoon" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CC02EB56-DF2A-4DBF-89DB-C60136C41B78}" name="Digester / covered lagoons" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{CFCF1518-11A1-4DAB-8850-4699547B9209}" name="Digester / covered lagoons" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A7C14051-C9CF-4AD7-B568-62D0DA4C6C88}" name="Liquid systems" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{14E75798-E773-4384-9856-BEB52763DFC8}" name="Liquid systems" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9BFB0B87-AF73-4199-A0F4-249625F3E94A}" name="Daily spread" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{1E1BAEC1-8F66-4698-B266-E544A9B86C3D}" name="Daily spread" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5B4CC1F9-79F9-4225-A482-8D9F2B38607D}" name="Composting (passive windrow)" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{8B59E468-F7A4-44DF-B374-097C483D5326}" name="Composting (passive windrow)" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C67915E4-55C4-4DFE-AC34-7FEF63096ABF}" name="Solid storage" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{6B7F802C-0201-408A-BEF5-CD2D19A9080D}" name="Solid storage" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{56A9FA80-890E-4119-B8C6-80060AFA757D}" name="Pit storage" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{8143B192-6129-465D-A688-665AF0B535FE}" name="Pit storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C1E464C9-BB3C-4349-80E5-E040EEFC92D3}" name="Deep litter" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{E82D2E9A-41C6-445C-BFB4-E1444428C570}" name="Deep litter" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6510F327-7673-48CD-949B-4E2593CC88C7}" name="Poultry manure with bedding" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{88073C9F-1A83-427D-856A-DB1534978205}" name="Poultry manure with bedding" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BED0BB92-704A-4D5B-915E-B535AA23FFE9}" name="Poultry manure without bedding" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{4FF593F6-8D3E-4B06-B5DB-C9209871B77B}" name="Poultry manure without bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{7F6B929D-02BF-42F7-A9BF-ECD48D8B5D37}" name="Direct processing" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{249F4794-93EE-4A09-B993-C22CAEC678F8}" name="Direct processing" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{829A2829-745F-4D05-93C4-6FD42C67E6D4}" name="Direct application" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{FFE83EF1-4D9B-45AC-91B4-64A2E71A2F50}" name="Direct application" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{54827D74-DE91-4D54-93AF-24C63D8E5FA6}" name="Pasture range and paddock" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{4CB4EB58-FA64-44C2-AA67-6810721CAC40}" name="Pasture range and paddock" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A855CCC3-ABEA-4445-8B01-8ED0F1FCCB98}" name="MAT raw" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{3095F771-5FAE-48A2-AF9C-2B56CD96483C}" name="MAT raw" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2461,16 +2682,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{AB3A5C90-13B8-4E18-8FA4-BB68BDBCA5BE}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{29AE98D8-CC96-471E-B1D3-FB22978A6B7C}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{77A1EB56-28D9-467A-AF37-B37086F57087}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{5AD13E31-F648-4032-B880-8C3DC06557B5}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF01B99A-E2BB-4F5D-82E2-8C5B51CF74AF}" name="EFNi &amp; EFN2Oi" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{59FE2A71-FC7A-47D0-AA83-D3562A6EB39B}" name="EFNi &amp; EFN2Oi" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2478,21 +2699,37 @@
 </table>
 </file>
 
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{BA8B56D7-73C1-4434-B635-62A4FE1B21AF}" name="Table_SourceData_DataQuality_TemporalRepresentativeness" displayName="Table_SourceData_DataQuality_TemporalRepresentativeness" ref="D265:F270" totalsRowShown="0">
+  <autoFilter ref="D265:F270" xr:uid="{9AD44602-D2F2-4D97-923C-A32E98F8C17A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{6441DED1-920D-4CB4-B8A8-3F0C5B739B56}" name="Description" dataDxfId="0" dataCellStyle="Content normal"/>
+    <tableColumn id="1" xr3:uid="{AA1DC1FA-EB99-4596-B85B-373F7C251A0D}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{CEAC8412-8D56-4472-9490-372300404E71}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ECEAE884-E3AA-4C6F-B76F-5EC80216329E}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{62DCCCF6-9623-46D4-8FAD-3F97A156B466}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7FC2ED6E-9CC3-451B-BB51-1CF60EA95BE7}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{6A37AD80-26B8-4BF8-ADF5-D6550355DD28}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{69FDD198-8517-445D-B48E-3D2F8192DDD6}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{4B8C4193-DBF9-40D7-BE6F-B61A78972A19}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CC167379-513B-4F97-B5CC-453590524E9E}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{D734512A-DF1F-4675-84DB-6631F0B5F09B}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2500,13 +2737,61 @@
 </table>
 </file>
 
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{A4AB1286-5DC9-4762-A6AA-D093231314F6}" name="Table_SourceData_DataQuality_SpatialRepresentativeness" displayName="Table_SourceData_DataQuality_SpatialRepresentativeness" ref="D274:F279" totalsRowShown="0">
+  <autoFilter ref="D274:F279" xr:uid="{95094D65-3E0E-45CE-A3F4-F41E74C11901}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EBBACF02-33BC-4292-8543-F247A435C522}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{B310906E-1AC5-4843-9892-59B23A1D23C2}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{589E59E0-58F2-42CE-8617-1665EFC533CA}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{C86C1717-3603-49EF-9C09-DA0C4735664F}" name="Table_SourceData_DataQuality_SampleSize" displayName="Table_SourceData_DataQuality_SampleSize" ref="D283:F288" totalsRowShown="0">
+  <autoFilter ref="D283:F288" xr:uid="{DE8F748C-E65A-4AA2-81BB-D28A432CF334}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{1BD732EC-E6B3-44AA-BFE9-9E2254CDCD8A}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{8DEAED7E-6A13-45F6-846B-44DE802BBE60}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{5C7CE100-C218-4681-9F3C-2FF959368A77}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{CA567294-FA43-4897-9A33-CB51AB292826}" name="Table_SourceData_DataQuality_Scope3" displayName="Table_SourceData_DataQuality_Scope3" ref="D292:F297" totalsRowShown="0">
+  <autoFilter ref="D292:F297" xr:uid="{43A1C4DA-75D1-45DF-BA9A-1798C2CC5A4B}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{5E552CA8-52EE-41D1-ABF8-8FB1356BEA62}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{2383AD31-3BF1-4EF2-B544-5DDF8FC65A08}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{10BC2248-A94C-48DC-90EC-B199EB163A27}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8E528ABB-A26F-400A-BD77-8DD10E99203E}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{5A12BF50-B2C0-4F28-B769-DF65D965FAE9}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2AF04A24-C2E5-40D4-A44B-0AD492D10AAC}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{4BF14B43-C5E4-43E5-94C6-5CC3A3727591}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2515,16 +2800,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AF4E352C-0731-4A89-995E-0577E0F81CAC}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{DD775225-E136-4188-80E7-4D6D9C573916}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C1590E77-49BB-4F5F-A3E4-8D21445CC724}" name="Gas">
+    <tableColumn id="1" xr3:uid="{76E3CEEF-940D-4F96-9826-4894969F6766}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8424FE5B-0604-45C7-8E88-6E3915DB6C5E}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{76A8CD4A-9663-4DC0-9557-E51650245E19}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2533,7 +2818,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C3E783B8-6109-4CA2-8525-8E3ACAC4A2E2}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{9367B7C6-11CC-4998-A676-0EA0F8A7CB13}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2542,19 +2827,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{076DDD46-7EB4-4141-ABC3-B1C9EA1E33AC}" name="Gas">
+    <tableColumn id="1" xr3:uid="{5AF6AFF8-7156-4068-AFA1-A05A77586EE1}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{641E9CD4-4DD0-4391-A5D8-16A02AA9505D}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{4A3CCAEC-4580-4A55-8150-10E53100F1D8}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B5D2251-1C02-432C-B625-2A8A6A7B78CC}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{F1FE2B8A-3DB9-435C-89C3-EE2E9DD4241C}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{33221A81-0123-4115-A3DB-31A52379BDDF}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{5131E514-D05A-475A-9713-A54EB9EB24AF}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DEC055F7-3C62-4999-8761-A614D18A2201}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{AF394157-5599-422B-89CD-3C15030D9ABC}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2563,7 +2848,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AB0AAAA7-F92F-42F5-85EE-5E3F3264F356}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{5F0D4774-559F-4D21-BE5C-CCE562DDF9FF}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2583,52 +2868,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6B14D34F-47D9-4E7B-8F67-CFF2BA3972F3}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{142CCBAE-686B-4EA5-A752-7B43B2E847A8}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{03D79397-427F-4BDD-85F7-C446814C4630}" name="MAT" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{ACA2244E-2A25-461B-8103-77F0B17AC271}" name="MAT" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{513FFB98-589A-4C52-B02E-C13C07167123}" name="MAP" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{EF3A0CD1-0E95-4732-8878-F26CFFAA5745}" name="MAP" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{851B3A05-D860-4BC9-8FF0-AA7455D1A0B6}" name="Frost days per year" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{5486BCB9-64F4-459D-8E1B-B9A9836223CD}" name="Frost days per year" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{111DCB69-2E86-452A-B93A-BB116EFF4325}" name="Elevation" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{D08F1118-3EE8-41F0-9822-F9358692BF2C}" name="Elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{EC9B3EBF-3D45-47C7-A0FC-3AAAB728216D}" name="MAP:PET" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{59390B9F-BBD8-4C3D-A119-7915AD070A8C}" name="MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DEE780F3-8FFA-489F-8BF5-29BB91E9B886}" name="Min temp" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{0B01CD16-6DBD-43A9-82CA-F5212C850250}" name="Min temp" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B796F2C1-4462-489B-B059-A97C3CB09E44}" name="Max temp" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{BFAF9C24-619D-4491-9D0B-DF338BE3E5E3}" name="Max temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{77FF4CA7-BCFB-4B5C-BCB0-CB746D9404FB}" name="Min rainfall" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{D7F3DAD5-7145-4A67-8FC9-2D27551FD5CD}" name="Min rainfall" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{70480799-57AD-475D-8EFB-ECBA87036E18}" name="Max rainfall" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{E77D8F4B-389D-4C0D-8D94-BC51C1C18896}" name="Max rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F20E603D-FAAB-4E85-8158-CCCAEF0C348A}" name="Min frost days" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{DEFFDA3B-EDA2-42E1-9850-2492F98E80CE}" name="Min frost days" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1CA64B37-B900-4123-9FA9-9F8F3122E9E6}" name="Max frost days" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{A6466F2B-43B8-4175-AEF1-A494CB1D1D19}" name="Max frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7C463F98-D060-4671-AAED-63888110DC70}" name="Min elevation" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{BC52070D-5AF4-474F-9883-B217986F2622}" name="Min elevation" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{DDE870B0-2FB3-449F-A8E3-315A6DD8565C}" name="Max elevation" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{861834F0-AF8C-4233-B4CF-01A3E8DB9BDC}" name="Max elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B5E2ADB7-D4D8-4A56-B4DC-C29288E8C038}" name="Min MAP:PET" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{921A837F-DDC9-4B53-9BF3-BFDC1DFD52DD}" name="Min MAP:PET" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{05917C51-1048-4C05-B02E-F19C0EBAB3ED}" name="Max MAP:PET" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{67A2EF78-7EE9-4443-8505-B027EAC097D7}" name="Max MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2637,16 +2922,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F669204B-D068-44A2-9480-8A66165B3EAE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{06624F3F-9605-4A37-9233-97F41645AA6A}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C09B5C83-2A18-415A-8927-96C97C2B88AA}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{1416A4B8-0477-4863-A2EB-08D05A0719A3}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EC38C61-E15D-47AA-A64C-8434A7A2E790}" name="Wet or Dry Zone" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{FBA0391C-8096-44D4-9318-58AE5A117EA6}" name="Wet or Dry Zone" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2655,7 +2940,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4CFAC30E-767E-441C-9CAB-02CF9F402801}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{1B211F2B-68EE-405C-B7A4-7A621E0786D1}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2663,16 +2948,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3D3FC7A5-5655-47CF-8CEA-D7AA25457E23}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{8CBC1D43-6B70-48EA-964A-AE7905EA8045}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8EB813D0-7500-4271-8891-9B47195294BE}" name="MAT">
+    <tableColumn id="2" xr3:uid="{F955B53F-9C0C-4BBF-8A27-7D26986B3892}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F6C5B6B9-2851-4A79-9DA4-B963F74F1A73}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{3F76A906-5C61-497F-A5D4-E37963640E92}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16E5C636-186F-4127-9D67-5061CE148DA7}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{39D12633-A5DE-4059-AD8B-4A37B67A6CA1}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2681,7 +2966,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4B53211D-6A46-4AAE-B337-B836933DB48C}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{1B6C97AB-258B-4141-911E-681B0F45FD41}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2689,16 +2974,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{52788624-E238-4310-9AA8-0A882B964680}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{D8F62325-70AC-4FE5-8B91-C8B0897947C8}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{59BA997A-F6DC-4009-8461-7AB550228F23}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{EA8B3174-62BF-4413-A1D1-AD7F17E48855}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB9C46E3-D112-4861-BD27-D94C521ECF35}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{B53FD3EB-06E6-4D73-B2A4-D010E7F5AC22}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0051EE80-A4A4-414E-9CC7-9F2ED58BBBD9}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{C2A3929C-6753-4380-8588-A8AF6B353127}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3233,7 +3518,7 @@
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
       <c r="J7" s="28">
-        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[1]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[1]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[1]!Table_SourceData_DataQuality_SampleSize[ID],[1]!Table_SourceData_DataQuality_SampleSize[Score])</f>
+        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</f>
         <v>12</v>
       </c>
     </row>
@@ -3257,8 +3542,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5D8088-0800-4A2B-8100-637E09B303F8}">
-  <dimension ref="A1:BY259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87287D1F-70E7-47A5-BFDD-AB62CDFC8688}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:BY297"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.875" style="11" customWidth="1"/>
@@ -3292,9 +3580,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+    </row>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="29" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -3330,7 +3623,9 @@
       <c r="BM5" s="14"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+      <c r="A6" s="30" t="s">
+        <v>91</v>
+      </c>
       <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
@@ -3342,125 +3637,131 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="A7" s="31" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
       <c r="D7" s="17" t="str" cm="1">
-        <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>New South Wales</v>
+        <f t="array" aca="1" ref="D7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E7" s="17" t="str" cm="1">
-        <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>New South Wales</v>
+        <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F7" s="17" t="str" cm="1">
-        <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>NSW</v>
+        <f t="array" aca="1" ref="F7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="29" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
+      </c>
       <c r="D8" s="17" t="str" cm="1">
-        <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Australian Capital Territory</v>
+        <f t="array" aca="1" ref="D8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E8" s="17" t="str" cm="1">
-        <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>ACT</v>
+        <f t="array" aca="1" ref="E8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F8" s="17" t="str" cm="1">
-        <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>ACT</v>
+        <f t="array" aca="1" ref="F8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="D9" s="17" t="str" cm="1">
-        <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Victoria</v>
+        <f t="array" aca="1" ref="D9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E9" s="17" t="str" cm="1">
-        <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Victoria</v>
+        <f t="array" aca="1" ref="E9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F9" s="17" t="str" cm="1">
-        <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>VIC</v>
+        <f t="array" aca="1" ref="F9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="D10" s="17" t="str" cm="1">
-        <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Queensland</v>
+        <f t="array" aca="1" ref="D10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E10" s="17" t="str" cm="1">
-        <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Queensland</v>
+        <f t="array" aca="1" ref="E10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F10" s="17" t="str" cm="1">
-        <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>QLD</v>
+        <f t="array" aca="1" ref="F10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="D11" s="17" t="str" cm="1">
-        <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>South Australia</v>
+        <f t="array" aca="1" ref="D11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E11" s="17" t="str" cm="1">
-        <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>South Australia</v>
+        <f t="array" aca="1" ref="E11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F11" s="17" t="str" cm="1">
-        <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>SA</v>
+        <f t="array" aca="1" ref="F11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="BM11" s="14"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="D12" s="17" t="str" cm="1">
-        <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Western Australia</v>
+        <f t="array" aca="1" ref="D12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E12" s="17" t="str" cm="1">
-        <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Western Australia</v>
+        <f t="array" aca="1" ref="E12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F12" s="17" t="str" cm="1">
-        <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>WA</v>
+        <f t="array" aca="1" ref="F12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="BM12" s="14"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="D13" s="17" t="str" cm="1">
-        <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Tasmania</v>
+        <f t="array" aca="1" ref="D13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E13" s="17" t="str" cm="1">
-        <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Tasmania</v>
+        <f t="array" aca="1" ref="E13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F13" s="17" t="str" cm="1">
-        <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>TAS</v>
+        <f t="array" aca="1" ref="F13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="D14" s="17" t="str" cm="1">
-        <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Northern Territory</v>
+        <f t="array" aca="1" ref="D14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E14" s="17" t="str" cm="1">
-        <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Northern Territory</v>
+        <f t="array" aca="1" ref="E14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F14" s="17" t="str" cm="1">
-        <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>NT</v>
+        <f t="array" aca="1" ref="F14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3495,71 +3796,71 @@
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="D21" s="17" t="str" cm="1">
-        <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Bunbury</v>
+        <f t="array" aca="1" ref="D21" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="D22" s="17" t="str" cm="1">
-        <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Mandurah</v>
+        <f t="array" aca="1" ref="D22" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="D23" s="17" t="str" cm="1">
-        <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - Inner</v>
+        <f t="array" aca="1" ref="D23" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="D24" s="17" t="str" cm="1">
-        <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - North East</v>
+        <f t="array" aca="1" ref="D24" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="D25" s="17" t="str" cm="1">
-        <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - North West</v>
+        <f t="array" aca="1" ref="D25" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="D26" s="17" t="str" cm="1">
-        <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - South East</v>
+        <f t="array" aca="1" ref="D26" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="D27" s="17" t="str" cm="1">
-        <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - South West</v>
+        <f t="array" aca="1" ref="D27" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="D28" s="17" t="str" cm="1">
-        <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Wheat Belt</v>
+        <f t="array" aca="1" ref="D28" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="D29" s="17" t="str" cm="1">
-        <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Outback (North)</v>
+        <f t="array" aca="1" ref="D29" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="D30" s="17" t="str" cm="1">
-        <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Outback (South)</v>
+        <f t="array" aca="1" ref="D30" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3597,92 +3898,99 @@
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="D37" s="17" t="str" cm="1">
-        <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CO2</v>
-      </c>
-      <c r="E37" s="17" cm="1">
-        <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D37" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E37" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="D38" s="17" t="str" cm="1">
-        <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CH4</v>
-      </c>
-      <c r="E38" s="17" cm="1">
-        <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
+        <f t="array" aca="1" ref="D38" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E38" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="D39" s="17" t="str" cm="1">
-        <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>N2O</v>
-      </c>
-      <c r="E39" s="17" cm="1">
-        <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>265</v>
+        <f t="array" aca="1" ref="D39" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E39" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="D40" s="17" t="str" cm="1">
-        <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CF4</v>
-      </c>
-      <c r="E40" s="17" cm="1">
-        <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>6630</v>
+        <f t="array" aca="1" ref="D40" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E40" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="D41" s="17" t="str" cm="1">
-        <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>C2F6</v>
-      </c>
-      <c r="E41" s="17" cm="1">
-        <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>12200</v>
+        <f t="array" aca="1" ref="D41" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E41" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
       <c r="D42" s="17" t="str" cm="1">
-        <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>SF6</v>
-      </c>
-      <c r="E42" s="17" cm="1">
-        <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>22800</v>
+        <f t="array" aca="1" ref="D42" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E42" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
       <c r="D43" s="17" t="str" cm="1">
-        <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>NF3</v>
-      </c>
-      <c r="E43" s="17" cm="1">
-        <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>17200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <f t="array" aca="1" ref="D43" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E43" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E43" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="10"/>
+    </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10"/>
       <c r="D45" s="16" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="10"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
       <c r="D47" s="17" t="s">
         <v>18</v>
       </c>
@@ -3700,191 +4008,210 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="10"/>
       <c r="D48" s="17" t="str" cm="1">
-        <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO2</v>
+        <f t="array" aca="1" ref="D48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E48" s="17" t="str" cm="1">
-        <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/12</v>
-      </c>
-      <c r="F48" s="17" cm="1">
-        <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G48" s="17" cm="1">
-        <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H48" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.6666666666666665</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="10"/>
       <c r="D49" s="17" t="str" cm="1">
-        <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CH4</v>
+        <f t="array" aca="1" ref="D49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E49" s="17" t="str" cm="1">
-        <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>16/12</v>
-      </c>
-      <c r="F49" s="17" cm="1">
-        <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>16</v>
-      </c>
-      <c r="G49" s="17" cm="1">
-        <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H49" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.3333333333333333</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F49" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="10"/>
       <c r="D50" s="17" t="str" cm="1">
-        <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>N2O</v>
+        <f t="array" aca="1" ref="D50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E50" s="17" t="str" cm="1">
-        <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/28</v>
-      </c>
-      <c r="F50" s="17" cm="1">
-        <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G50" s="17" cm="1">
-        <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
-      </c>
-      <c r="H50" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.5714285714285714</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F50" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10"/>
       <c r="D51" s="17" t="str" cm="1">
-        <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>Nox</v>
+        <f t="array" aca="1" ref="D51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E51" s="17" t="str" cm="1">
-        <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>46/14</v>
-      </c>
-      <c r="F51" s="17" cm="1">
-        <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>46</v>
-      </c>
-      <c r="G51" s="17" cm="1">
-        <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14</v>
-      </c>
-      <c r="H51" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.2857142857142856</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F51" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="10"/>
       <c r="D52" s="17" t="str" cm="1">
-        <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO</v>
+        <f t="array" aca="1" ref="D52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E52" s="17" t="str" cm="1">
-        <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28/12</v>
-      </c>
-      <c r="F52" s="17" cm="1">
-        <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
-      </c>
-      <c r="G52" s="17" cm="1">
-        <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H52" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>2.3333333333333335</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F52" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="10"/>
       <c r="D53" s="17" t="str" cm="1">
-        <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO2 Lime</v>
+        <f t="array" aca="1" ref="D53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E53" s="17" t="str" cm="1">
-        <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/12</v>
-      </c>
-      <c r="F53" s="17" cm="1">
-        <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G53" s="17" cm="1">
-        <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H53" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.6666666666666665</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F53" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="10"/>
       <c r="D54" s="17" t="str" cm="1">
-        <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>NMVOC</v>
+        <f t="array" aca="1" ref="D54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E54" s="17" t="str" cm="1">
-        <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14/12</v>
-      </c>
-      <c r="F54" s="17" cm="1">
-        <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14</v>
-      </c>
-      <c r="G54" s="17" cm="1">
-        <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H54" s="17">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.1666666666666667</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F54" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="17" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="10"/>
+    </row>
+    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="10"/>
+    </row>
+    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="10"/>
       <c r="D57" s="16" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="10"/>
       <c r="D59" s="19" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10"/>
       <c r="D60" s="19" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="10"/>
       <c r="D61" s="19" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="10"/>
+    </row>
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10"/>
       <c r="D63" s="17" t="s">
         <v>24</v>
       </c>
@@ -3892,189 +4219,219 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10"/>
       <c r="D64" s="17" t="str" cm="1">
-        <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical montane</v>
+        <f t="array" aca="1" ref="D64" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E64" s="17" t="str" cm="1">
-        <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E64" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="10"/>
       <c r="D65" s="17" t="str" cm="1">
-        <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical wet</v>
+        <f t="array" aca="1" ref="D65" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E65" s="17" t="str" cm="1">
-        <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E65" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="10"/>
       <c r="D66" s="17" t="str" cm="1">
-        <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical moist</v>
+        <f t="array" aca="1" ref="D66" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E66" s="17" t="str" cm="1">
-        <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E66" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="10"/>
       <c r="D67" s="17" t="str" cm="1">
-        <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical dry</v>
+        <f t="array" aca="1" ref="D67" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E67" s="17" t="str" cm="1">
-        <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E67" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="10"/>
       <c r="D68" s="17" t="str" cm="1">
-        <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist</v>
+        <f t="array" aca="1" ref="D68" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E68" s="17" t="str" cm="1">
-        <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E68" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="10"/>
       <c r="D69" s="17" t="str" cm="1">
-        <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry</v>
+        <f t="array" aca="1" ref="D69" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E69" s="17" t="str" cm="1">
-        <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E69" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="10"/>
       <c r="D70" s="17" t="str" cm="1">
-        <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist</v>
+        <f t="array" aca="1" ref="D70" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E70" s="17" t="str" cm="1">
-        <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E70" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="10"/>
       <c r="D71" s="17" t="str" cm="1">
-        <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry</v>
+        <f t="array" aca="1" ref="D71" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E71" s="17" t="str" cm="1">
-        <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E71" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="10"/>
       <c r="D72" s="17" t="str" cm="1">
-        <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist - low frost</v>
+        <f t="array" aca="1" ref="D72" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E72" s="17" t="str" cm="1">
-        <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E72" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="10"/>
       <c r="D73" s="17" t="str" cm="1">
-        <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry - low frost</v>
+        <f t="array" aca="1" ref="D73" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E73" s="17" t="str" cm="1">
-        <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E73" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="10"/>
       <c r="D74" s="17" t="str" cm="1">
-        <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist - high temp</v>
+        <f t="array" aca="1" ref="D74" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E74" s="17" t="str" cm="1">
-        <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E74" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10"/>
       <c r="D75" s="17" t="str" cm="1">
-        <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry - high temp</v>
+        <f t="array" aca="1" ref="D75" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E75" s="17" t="str" cm="1">
-        <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E75" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="10"/>
       <c r="D76" s="17" t="str" cm="1">
-        <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist - low frost</v>
+        <f t="array" aca="1" ref="D76" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E76" s="17" t="str" cm="1">
-        <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E76" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="10"/>
       <c r="D77" s="17" t="str" cm="1">
-        <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry - low frost</v>
+        <f t="array" aca="1" ref="D77" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E77" s="17" t="str" cm="1">
-        <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E77" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="10"/>
+    </row>
+    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="10"/>
+    </row>
+    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="10"/>
+    </row>
+    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="10"/>
       <c r="D81" s="16" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="10"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="10"/>
       <c r="D83" s="19" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="10"/>
       <c r="D84" s="19" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10"/>
       <c r="D85" s="19" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="10"/>
       <c r="D86" s="19" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="10"/>
       <c r="D87" s="19" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10"/>
+    </row>
+    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="10"/>
       <c r="D89" s="17" t="s">
         <v>24</v>
       </c>
@@ -4125,588 +4482,611 @@
       </c>
       <c r="T89" s="17"/>
     </row>
-    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="10"/>
       <c r="D90" s="17" t="str" cm="1">
-        <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical montane</v>
+        <f t="array" aca="1" ref="D90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E90" s="17" t="str" cm="1">
-        <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F90" s="17" t="str" cm="1">
-        <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G90" s="17" t="str" cm="1">
-        <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H90" s="17" t="str" cm="1">
-        <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1000 m</v>
+        <f t="array" aca="1" ref="H90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I90" s="17" t="str" cm="1">
-        <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J90" s="17" cm="1">
-        <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K90" s="17" cm="1">
-        <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L90" s="17" cm="1">
-        <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M90" s="17" cm="1">
-        <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N90" s="17" cm="1">
-        <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O90" s="17" cm="1">
-        <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P90" s="17" cm="1">
-        <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000</v>
-      </c>
-      <c r="Q90" s="17" cm="1">
-        <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R90" s="17" cm="1">
-        <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S90" s="17" cm="1">
-        <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S90" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T90" s="17"/>
     </row>
-    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="10"/>
       <c r="D91" s="17" t="str" cm="1">
-        <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical wet</v>
+        <f t="array" aca="1" ref="D91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E91" s="17" t="str" cm="1">
-        <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F91" s="17" t="str" cm="1">
-        <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 2000 mm</v>
+        <f t="array" aca="1" ref="F91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G91" s="17" t="str" cm="1">
-        <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H91" s="17" t="str" cm="1">
-        <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I91" s="17" t="str" cm="1">
-        <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J91" s="17" cm="1">
-        <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K91" s="17" cm="1">
-        <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L91" s="17" cm="1">
-        <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>2000.001</v>
-      </c>
-      <c r="M91" s="17" cm="1">
-        <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N91" s="17" cm="1">
-        <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O91" s="17" cm="1">
-        <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P91" s="17" cm="1">
-        <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q91" s="17" cm="1">
-        <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R91" s="17" cm="1">
-        <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S91" s="17" cm="1">
-        <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S91" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T91" s="17"/>
     </row>
-    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="10"/>
       <c r="D92" s="17" t="str" cm="1">
-        <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical moist</v>
+        <f t="array" aca="1" ref="D92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E92" s="17" t="str" cm="1">
-        <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F92" s="17" t="str" cm="1">
-        <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1000 mm - ≤ 2000 mm</v>
+        <f t="array" aca="1" ref="F92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G92" s="17" t="str" cm="1">
-        <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H92" s="17" t="str" cm="1">
-        <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I92" s="17" t="str" cm="1">
-        <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J92" s="17" cm="1">
-        <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K92" s="17" cm="1">
-        <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L92" s="17" cm="1">
-        <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000.001</v>
-      </c>
-      <c r="M92" s="17" cm="1">
-        <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>2000</v>
-      </c>
-      <c r="N92" s="17" cm="1">
-        <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O92" s="17" cm="1">
-        <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P92" s="17" cm="1">
-        <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q92" s="17" cm="1">
-        <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R92" s="17" cm="1">
-        <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S92" s="17" cm="1">
-        <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S92" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T92" s="17"/>
     </row>
-    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="10"/>
       <c r="D93" s="17" t="str" cm="1">
-        <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical dry</v>
+        <f t="array" aca="1" ref="D93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E93" s="17" t="str" cm="1">
-        <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F93" s="17" t="str" cm="1">
-        <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 mm</v>
+        <f t="array" aca="1" ref="F93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G93" s="17" t="str" cm="1">
-        <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H93" s="17" t="str" cm="1">
-        <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I93" s="17" t="str" cm="1">
-        <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J93" s="17" cm="1">
-        <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K93" s="17" cm="1">
-        <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L93" s="17" cm="1">
-        <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M93" s="17" cm="1">
-        <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000</v>
-      </c>
-      <c r="N93" s="17" cm="1">
-        <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O93" s="17" cm="1">
-        <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P93" s="17" cm="1">
-        <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q93" s="17" cm="1">
-        <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R93" s="17" cm="1">
-        <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S93" s="17" cm="1">
-        <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S93" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T93" s="17"/>
     </row>
-    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="10"/>
       <c r="D94" s="17" t="str" cm="1">
-        <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist</v>
+        <f t="array" aca="1" ref="D94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E94" s="17" t="str" cm="1">
-        <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 10 C</v>
+        <f t="array" aca="1" ref="E94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F94" s="17" t="str" cm="1">
-        <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G94" s="17" t="str" cm="1">
-        <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H94" s="17" t="str" cm="1">
-        <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I94" s="17" t="str" cm="1">
-        <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1</v>
-      </c>
-      <c r="J94" s="17" cm="1">
-        <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10.000999999999999</v>
-      </c>
-      <c r="K94" s="17" cm="1">
-        <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L94" s="17" cm="1">
-        <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M94" s="17" cm="1">
-        <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N94" s="17" cm="1">
-        <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O94" s="17" cm="1">
-        <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P94" s="17" cm="1">
-        <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q94" s="17" cm="1">
-        <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R94" s="17" cm="1">
-        <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="S94" s="17" cm="1">
-        <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S94" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T94" s="17"/>
     </row>
-    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="10"/>
       <c r="D95" s="17" t="str" cm="1">
-        <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry</v>
+        <f t="array" aca="1" ref="D95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E95" s="17" t="str" cm="1">
-        <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 10 C</v>
+        <f t="array" aca="1" ref="E95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F95" s="17" t="str" cm="1">
-        <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G95" s="17" t="str" cm="1">
-        <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H95" s="17" t="str" cm="1">
-        <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I95" s="17" t="str" cm="1">
-        <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1</v>
-      </c>
-      <c r="J95" s="17" cm="1">
-        <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10.000999999999999</v>
-      </c>
-      <c r="K95" s="17" cm="1">
-        <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L95" s="17" cm="1">
-        <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M95" s="17" cm="1">
-        <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N95" s="17" cm="1">
-        <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O95" s="17" cm="1">
-        <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P95" s="17" cm="1">
-        <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q95" s="17" cm="1">
-        <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R95" s="17" cm="1">
-        <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S95" s="17" cm="1">
-        <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="I95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S95" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T95" s="17"/>
     </row>
-    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10"/>
       <c r="D96" s="17" t="str" cm="1">
-        <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist</v>
+        <f t="array" aca="1" ref="D96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E96" s="17" t="str" cm="1">
-        <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 0 C - ≤ 10 C</v>
+        <f t="array" aca="1" ref="E96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F96" s="17" t="str" cm="1">
-        <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G96" s="17" t="str" cm="1">
-        <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H96" s="17" t="str" cm="1">
-        <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I96" s="17" t="str" cm="1">
-        <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1</v>
-      </c>
-      <c r="J96" s="17" cm="1">
-        <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="K96" s="17" cm="1">
-        <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10</v>
-      </c>
-      <c r="L96" s="17" cm="1">
-        <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M96" s="17" cm="1">
-        <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N96" s="17" cm="1">
-        <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O96" s="17" cm="1">
-        <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P96" s="17" cm="1">
-        <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q96" s="17" cm="1">
-        <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R96" s="17" cm="1">
-        <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="S96" s="17" cm="1">
-        <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S96" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T96" s="17"/>
     </row>
-    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10"/>
       <c r="D97" s="17" t="str" cm="1">
-        <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry</v>
+        <f t="array" aca="1" ref="D97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E97" s="17" t="str" cm="1">
-        <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 0 C - ≤ 10 C</v>
+        <f t="array" aca="1" ref="E97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F97" s="17" t="str" cm="1">
-        <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G97" s="17" t="str" cm="1">
-        <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H97" s="17" t="str" cm="1">
-        <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I97" s="17" t="str" cm="1">
-        <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1</v>
-      </c>
-      <c r="J97" s="17" cm="1">
-        <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="K97" s="17" cm="1">
-        <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10</v>
-      </c>
-      <c r="L97" s="17" cm="1">
-        <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M97" s="17" cm="1">
-        <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N97" s="17" cm="1">
-        <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O97" s="17" cm="1">
-        <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P97" s="17" cm="1">
-        <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q97" s="17" cm="1">
-        <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R97" s="17" cm="1">
-        <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S97" s="17" cm="1">
-        <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="I97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S97" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T97" s="17"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="10"/>
+    </row>
+    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="10"/>
       <c r="D99" s="20" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="10"/>
       <c r="D100" s="20" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="10"/>
       <c r="D101" s="20" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="10"/>
       <c r="D102" s="20" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="10"/>
       <c r="D103" s="20"/>
     </row>
-    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10"/>
+    </row>
+    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10"/>
       <c r="D105" s="16" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10"/>
       <c r="D107" s="19" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10"/>
+    </row>
+    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="10"/>
       <c r="D109" s="17" t="s">
         <v>41</v>
       </c>
@@ -4720,87 +5100,99 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="10"/>
       <c r="D110" s="17" t="str" cm="1">
-        <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Warm</v>
+        <f t="array" aca="1" ref="D110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E110" s="17" t="str" cm="1">
-        <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>≥ 26 C</v>
-      </c>
-      <c r="F110" s="17" cm="1">
-        <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>26</v>
-      </c>
-      <c r="G110" s="17" cm="1">
-        <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>999999</v>
-      </c>
-    </row>
-    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F110" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G110" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="10"/>
       <c r="D111" s="17" t="str" cm="1">
-        <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Temperate</v>
+        <f t="array" aca="1" ref="D111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E111" s="17" t="str" cm="1">
-        <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>15 - 25 C</v>
-      </c>
-      <c r="F111" s="17" cm="1">
-        <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>15</v>
-      </c>
-      <c r="G111" s="17" cm="1">
-        <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>25.998999999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G111" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="10"/>
       <c r="D112" s="17" t="str" cm="1">
-        <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Cool</v>
+        <f t="array" aca="1" ref="D112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E112" s="17" t="str" cm="1">
-        <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>≤ 14 C</v>
-      </c>
-      <c r="F112" s="17" cm="1">
-        <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="G112" s="17" cm="1">
-        <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>14.999000000000001</v>
-      </c>
-    </row>
-    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G112" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10"/>
+    </row>
+    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="10"/>
+    </row>
+    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="10"/>
       <c r="D115" s="16" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
       <c r="BN115" s="11"/>
     </row>
-    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="10"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
       <c r="BN116" s="11"/>
     </row>
-    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10"/>
       <c r="D117" s="19" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
       <c r="BN117" s="11"/>
     </row>
-    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="10"/>
       <c r="BN118" s="11"/>
     </row>
-    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="10"/>
       <c r="D119" s="17" t="s">
         <v>44</v>
       </c>
@@ -4815,62 +5207,72 @@
       </c>
       <c r="BN119" s="11"/>
     </row>
-    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="10"/>
       <c r="D120" s="17" t="str" cm="1">
-        <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="D120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="E120" s="17" t="str" cm="1">
-        <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Annual rainfall &gt; 600mm</v>
-      </c>
-      <c r="F120" s="17" cm="1">
-        <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>600.00099999999998</v>
-      </c>
-      <c r="G120" s="17" cm="1">
-        <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="E120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F120" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G120" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="BN120" s="11"/>
     </row>
-    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="10"/>
       <c r="D121" s="17" t="str" cm="1">
-        <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="D121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="E121" s="17" t="str" cm="1">
-        <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Annual rainfall ≤ 600mm</v>
-      </c>
-      <c r="F121" s="17" cm="1">
-        <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="G121" s="17" cm="1">
-        <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>600</v>
+        <f t="array" aca="1" ref="E121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F121" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G121" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="BN121" s="11"/>
     </row>
-    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="10"/>
       <c r="BN122" s="11"/>
     </row>
-    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="10"/>
+    </row>
+    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="10"/>
       <c r="D124" s="16" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="10"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="10"/>
+    </row>
+    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="10"/>
       <c r="D127" s="17" t="s">
         <v>46</v>
       </c>
@@ -4878,43 +5280,52 @@
         <v>47</v>
       </c>
     </row>
-    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="10"/>
       <c r="D128" s="17" t="str" cm="1">
-        <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Leaching occurs</v>
+        <f t="array" aca="1" ref="D128" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
       </c>
       <c r="E128" s="17" t="str" cm="1">
-        <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
-      </c>
-    </row>
-    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E128" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="10"/>
       <c r="D129" s="17" t="str" cm="1">
-        <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Leaching does not occur</v>
+        <f t="array" aca="1" ref="D129" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
       </c>
       <c r="E129" s="17" t="str" cm="1">
-        <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
-      </c>
-    </row>
-    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E129" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="10"/>
+    </row>
+    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="10"/>
+    </row>
+    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="10"/>
       <c r="D132" s="16" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E132" s="21"/>
     </row>
-    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="10"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E133" s="21"/>
     </row>
-    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="10"/>
       <c r="D134" s="10" t="s">
         <v>48</v>
       </c>
@@ -4922,28 +5333,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="10"/>
       <c r="D135" s="10" t="str" cm="1">
-        <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>Yes - in leaching zone</v>
-      </c>
-      <c r="E135" s="10" cm="1">
-        <f t="array" ref="E135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D135" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E135" s="10" t="str" cm="1">
+        <f t="array" aca="1" ref="E135" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="10"/>
       <c r="D136" s="15" t="str" cm="1">
-        <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>No - not in leaching zone</v>
-      </c>
-      <c r="E136" s="17" cm="1">
-        <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D136" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E136" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E136" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="10"/>
+    </row>
+    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="10"/>
       <c r="BN138" s="11"/>
       <c r="BO138" s="11"/>
       <c r="BP138" s="11"/>
@@ -4957,7 +5373,8 @@
       <c r="BX138" s="11"/>
       <c r="BY138" s="11"/>
     </row>
-    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="10"/>
       <c r="D139" s="16" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
@@ -4975,7 +5392,8 @@
       <c r="BX139" s="11"/>
       <c r="BY139" s="11"/>
     </row>
-    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="10"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
@@ -4993,14 +5411,16 @@
       <c r="BX140" s="11"/>
       <c r="BY140" s="11"/>
     </row>
-    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="10"/>
       <c r="D141" s="19" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
       <c r="BN141" s="11"/>
     </row>
-    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="10"/>
       <c r="D142" s="17" t="s">
         <v>50</v>
       </c>
@@ -5009,85 +5429,96 @@
       </c>
       <c r="BN142" s="11"/>
     </row>
-    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="10"/>
       <c r="D143" s="17" t="str" cm="1">
-        <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="E143" s="17" cm="1">
-        <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="D143" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E143" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E143" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN143" s="11"/>
     </row>
-    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="10"/>
       <c r="D144" s="15" t="str" cm="1">
-        <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Drip irrigation</v>
-      </c>
-      <c r="E144" s="17" cm="1">
-        <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="D144" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E144" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E144" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN144" s="11"/>
     </row>
-    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="10"/>
       <c r="D145" s="15" t="str" cm="1">
-        <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Sprinkler irrigation</v>
-      </c>
-      <c r="E145" s="17" cm="1">
-        <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D145" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E145" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E145" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN145" s="11"/>
     </row>
-    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="10"/>
       <c r="D146" s="15" t="str" cm="1">
-        <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Surface irrigation</v>
-      </c>
-      <c r="E146" s="17" cm="1">
-        <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D146" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E146" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E146" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN146" s="11"/>
     </row>
-    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="10"/>
       <c r="D147" s="15" t="str" cm="1">
-        <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Other irrigation</v>
-      </c>
-      <c r="E147" s="17" cm="1">
-        <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D147" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E147" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E147" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN147" s="11"/>
     </row>
-    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="10"/>
       <c r="BN148" s="11"/>
     </row>
-    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="10"/>
       <c r="BN149" s="11"/>
     </row>
-    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="10"/>
       <c r="D150" s="16" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
       <c r="BN150" s="11"/>
     </row>
-    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="10"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
       <c r="BN151" s="11"/>
     </row>
-    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="10"/>
       <c r="BN152" s="11"/>
     </row>
-    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="10"/>
       <c r="D153" s="17" t="s">
         <v>51</v>
       </c>
@@ -5106,14 +5537,15 @@
       <c r="BL153" s="14"/>
       <c r="BM153" s="14"/>
     </row>
-    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="10"/>
       <c r="D154" s="17" t="str" cm="1">
-        <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>International scope 3 database</v>
-      </c>
-      <c r="E154" s="17" cm="1">
-        <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D154" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E154" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E154" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
       </c>
       <c r="BC154" s="14"/>
       <c r="BD154" s="14"/>
@@ -5127,14 +5559,15 @@
       <c r="BL154" s="14"/>
       <c r="BM154" s="14"/>
     </row>
-    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="10"/>
       <c r="D155" s="17" t="str" cm="1">
-        <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Australian scope 3 database</v>
-      </c>
-      <c r="E155" s="17" cm="1">
-        <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="D155" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E155" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E155" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
       </c>
       <c r="BC155" s="14"/>
       <c r="BD155" s="14"/>
@@ -5148,38 +5581,45 @@
       <c r="BL155" s="14"/>
       <c r="BM155" s="14"/>
     </row>
-    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="10"/>
       <c r="D156" s="17" t="str" cm="1">
-        <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>State or regional scope 3 database</v>
-      </c>
-      <c r="E156" s="17" cm="1">
-        <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D156" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E156" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E156" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="10"/>
       <c r="D157" s="17" t="str" cm="1">
-        <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Emissions intensity calculated from approved method</v>
-      </c>
-      <c r="E157" s="17" cm="1">
-        <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D157" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E157" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E157" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="10"/>
       <c r="D158" s="17" t="str" cm="1">
-        <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Verified credential matching ISO14067</v>
-      </c>
-      <c r="E158" s="17" cm="1">
-        <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <f t="array" aca="1" ref="D158" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E158" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E158" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="10"/>
+    </row>
+    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="10"/>
+    </row>
     <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="16" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
@@ -5379,288 +5819,288 @@
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="17" t="str" cm="1">
-        <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated pasture</v>
-      </c>
-      <c r="E187" s="17" cm="1">
-        <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.8999999999999999E-3</v>
+        <f t="array" aca="1" ref="D187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E187" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F187" s="17" t="str" cm="1">
-        <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G187" s="17" t="str" cm="1">
-        <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H187" s="17" t="str" cm="1">
-        <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="17" t="str" cm="1">
-        <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated crop</v>
-      </c>
-      <c r="E188" s="17" cm="1">
-        <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>7.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E188" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F188" s="17" t="str" cm="1">
-        <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G188" s="17" t="str" cm="1">
-        <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H188" s="17" t="str" cm="1">
-        <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="17" t="str" cm="1">
-        <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E189" s="17" cm="1">
-        <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E189" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F189" s="17" t="str" cm="1">
-        <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G189" s="17" t="str" cm="1">
-        <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H189" s="17" t="str" cm="1">
-        <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="H189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="17" t="str" cm="1">
-        <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E190" s="17" cm="1">
-        <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E190" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F190" s="17" t="str" cm="1">
-        <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G190" s="17" t="str" cm="1">
-        <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H190" s="17" t="str" cm="1">
-        <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="H190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="17" t="str" cm="1">
-        <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (low rainfall)</v>
-      </c>
-      <c r="E191" s="17" cm="1">
-        <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.8999999999999998E-3</v>
+        <f t="array" aca="1" ref="D191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E191" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F191" s="17" t="str" cm="1">
-        <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G191" s="17" t="str" cm="1">
-        <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H191" s="17" t="str" cm="1">
-        <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="H191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="17" t="str" cm="1">
-        <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (high rainfall)</v>
-      </c>
-      <c r="E192" s="17" cm="1">
-        <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>8.0000000000000002E-3</v>
+        <f t="array" aca="1" ref="D192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E192" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F192" s="17" t="str" cm="1">
-        <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G192" s="17" t="str" cm="1">
-        <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H192" s="17" t="str" cm="1">
-        <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="H192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="17" t="str" cm="1">
-        <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
-      </c>
-      <c r="E193" s="17" cm="1">
-        <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.9900000000000001E-2</v>
+        <f t="array" aca="1" ref="D193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E193" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F193" s="17" t="str" cm="1">
-        <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
+        <f t="array" aca="1" ref="F193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G193" s="17" t="str" cm="1">
-        <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H193" s="17" t="str" cm="1">
-        <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="17" t="str" cm="1">
-        <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
-      </c>
-      <c r="E194" s="17" cm="1">
-        <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.3E-3</v>
+        <f t="array" aca="1" ref="D194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E194" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F194" s="17" t="str" cm="1">
-        <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
+        <f t="array" aca="1" ref="F194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G194" s="17" t="str" cm="1">
-        <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H194" s="17" t="str" cm="1">
-        <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="17" t="str" cm="1">
-        <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
-      </c>
-      <c r="E195" s="17" cm="1">
-        <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>6.4000000000000003E-3</v>
+        <f t="array" aca="1" ref="D195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E195" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F195" s="17" t="str" cm="1">
-        <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
+        <f t="array" aca="1" ref="F195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G195" s="17" t="str" cm="1">
-        <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H195" s="17" t="str" cm="1">
-        <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="17" t="str" cm="1">
-        <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (continuous flooding)</v>
-      </c>
-      <c r="E196" s="17" cm="1">
-        <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>3.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E196" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F196" s="17" t="str" cm="1">
-        <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
+        <f t="array" aca="1" ref="F196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G196" s="17" t="str" cm="1">
-        <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Continuous flooding</v>
+        <f t="array" aca="1" ref="G196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H196" s="17" t="str" cm="1">
-        <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="197" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D197" s="17" t="str" cm="1">
-        <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
-      </c>
-      <c r="E197" s="17" cm="1">
-        <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E197" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F197" s="17" t="str" cm="1">
-        <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
+        <f t="array" aca="1" ref="F197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G197" s="17" t="str" cm="1">
-        <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Single and multiple drainage, or alternate wetting and drying</v>
+        <f t="array" aca="1" ref="G197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H197" s="17" t="str" cm="1">
-        <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="198" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D198" s="17" t="str" cm="1">
-        <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
-      </c>
-      <c r="E198" s="17" cm="1">
-        <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.5999999999999999E-3</v>
+        <f t="array" aca="1" ref="D198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E198" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F198" s="17" t="str" cm="1">
-        <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
+        <f t="array" aca="1" ref="F198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G198" s="17" t="str" cm="1">
-        <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H198" s="17" t="str" cm="1">
-        <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="199" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D199" s="17" t="str" cm="1">
-        <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
-      </c>
-      <c r="E199" s="17" cm="1">
-        <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E199" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F199" s="17" t="str" cm="1">
-        <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
+        <f t="array" aca="1" ref="F199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G199" s="17" t="str" cm="1">
-        <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H199" s="17" t="str" cm="1">
-        <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
@@ -5697,22 +6137,22 @@
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D207" s="17" t="str" cm="1">
-        <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-      <c r="E207" s="17" cm="1">
-        <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>6.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D207" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E207" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E207" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="208" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D208" s="15" t="str" cm="1">
-        <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-      <c r="E208" s="17" cm="1">
-        <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>2E-3</v>
+        <f t="array" aca="1" ref="D208" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E208" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E208" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="211" spans="4:5" x14ac:dyDescent="0.25">
@@ -5731,122 +6171,122 @@
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D213" s="17" t="str" cm="1">
-        <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>January</v>
+        <f t="array" aca="1" ref="D213" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E213" s="17" t="str" cm="1">
-        <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E213" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="214" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D214" s="15" t="str" cm="1">
-        <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>February</v>
+        <f t="array" aca="1" ref="D214" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E214" s="17" t="str" cm="1">
-        <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E214" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="215" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D215" s="15" t="str" cm="1">
-        <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>March</v>
+        <f t="array" aca="1" ref="D215" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E215" s="17" t="str" cm="1">
-        <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E215" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="216" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D216" s="15" t="str" cm="1">
-        <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>April</v>
+        <f t="array" aca="1" ref="D216" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E216" s="17" t="str" cm="1">
-        <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E216" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="217" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D217" s="15" t="str" cm="1">
-        <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>May</v>
+        <f t="array" aca="1" ref="D217" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E217" s="17" t="str" cm="1">
-        <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E217" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="218" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D218" s="15" t="str" cm="1">
-        <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>June</v>
+        <f t="array" aca="1" ref="D218" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E218" s="17" t="str" cm="1">
-        <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E218" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="219" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D219" s="15" t="str" cm="1">
-        <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>July</v>
+        <f t="array" aca="1" ref="D219" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E219" s="17" t="str" cm="1">
-        <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E219" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="220" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D220" s="15" t="str" cm="1">
-        <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>August</v>
+        <f t="array" aca="1" ref="D220" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E220" s="17" t="str" cm="1">
-        <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E220" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="221" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D221" s="15" t="str" cm="1">
-        <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>September</v>
+        <f t="array" aca="1" ref="D221" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E221" s="17" t="str" cm="1">
-        <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E221" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="222" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D222" s="15" t="str" cm="1">
-        <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>October</v>
+        <f t="array" aca="1" ref="D222" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E222" s="17" t="str" cm="1">
-        <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E222" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="223" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D223" s="15" t="str" cm="1">
-        <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>November</v>
+        <f t="array" aca="1" ref="D223" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E223" s="17" t="str" cm="1">
-        <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E223" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="224" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D224" s="15" t="str" cm="1">
-        <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>December</v>
+        <f t="array" aca="1" ref="D224" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E224" s="17" t="str" cm="1">
-        <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E224" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
@@ -5919,1256 +6359,1256 @@
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D232" s="17" t="str" cm="1">
-        <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
+        <f t="array" aca="1" ref="D232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
       <c r="E232" s="17" t="str" cm="1">
-        <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>≤10</v>
-      </c>
-      <c r="F232" s="17" cm="1">
-        <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.66</v>
-      </c>
-      <c r="G232" s="17" cm="1">
-        <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H232" s="17" cm="1">
-        <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="I232" s="17" cm="1">
-        <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J232" s="17" cm="1">
-        <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K232" s="17" cm="1">
-        <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L232" s="17" cm="1">
-        <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M232" s="17" cm="1">
-        <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N232" s="17" cm="1">
-        <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O232" s="17" cm="1">
-        <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P232" s="17" cm="1">
-        <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q232" s="17" cm="1">
-        <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R232" s="17" cm="1">
-        <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S232" s="17" cm="1">
-        <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>10</v>
+        <f t="array" aca="1" ref="E232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S232" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="233" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D233" s="15" t="str" cm="1">
-        <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E233" s="17" cm="1">
-        <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>11</v>
-      </c>
-      <c r="F233" s="17" cm="1">
-        <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.68</v>
-      </c>
-      <c r="G233" s="17" cm="1">
-        <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H233" s="17" cm="1">
-        <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.11</v>
-      </c>
-      <c r="I233" s="17" cm="1">
-        <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J233" s="17" cm="1">
-        <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K233" s="17" cm="1">
-        <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L233" s="17" cm="1">
-        <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M233" s="17" cm="1">
-        <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N233" s="17" cm="1">
-        <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O233" s="17" cm="1">
-        <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P233" s="17" cm="1">
-        <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q233" s="17" cm="1">
-        <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R233" s="17" cm="1">
-        <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S233" s="17" cm="1">
-        <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>11</v>
+        <f t="array" aca="1" ref="D233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S233" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="234" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D234" s="15" t="str" cm="1">
-        <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E234" s="17" cm="1">
-        <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>12</v>
-      </c>
-      <c r="F234" s="17" cm="1">
-        <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.7</v>
-      </c>
-      <c r="G234" s="17" cm="1">
-        <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H234" s="17" cm="1">
-        <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.13</v>
-      </c>
-      <c r="I234" s="17" cm="1">
-        <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J234" s="17" cm="1">
-        <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K234" s="17" cm="1">
-        <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L234" s="17" cm="1">
-        <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M234" s="17" cm="1">
-        <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N234" s="17" cm="1">
-        <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O234" s="17" cm="1">
-        <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P234" s="17" cm="1">
-        <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q234" s="17" cm="1">
-        <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R234" s="17" cm="1">
-        <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S234" s="17" cm="1">
-        <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>12</v>
+        <f t="array" aca="1" ref="D234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S234" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="235" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D235" s="15" t="str" cm="1">
-        <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E235" s="17" cm="1">
-        <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>13</v>
-      </c>
-      <c r="F235" s="17" cm="1">
-        <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.71</v>
-      </c>
-      <c r="G235" s="17" cm="1">
-        <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H235" s="17" cm="1">
-        <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="I235" s="17" cm="1">
-        <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J235" s="17" cm="1">
-        <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K235" s="17" cm="1">
-        <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L235" s="17" cm="1">
-        <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M235" s="17" cm="1">
-        <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N235" s="17" cm="1">
-        <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O235" s="17" cm="1">
-        <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P235" s="17" cm="1">
-        <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q235" s="17" cm="1">
-        <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R235" s="17" cm="1">
-        <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S235" s="17" cm="1">
-        <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>13</v>
+        <f t="array" aca="1" ref="D235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S235" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S235" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="236" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D236" s="15" t="str" cm="1">
-        <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E236" s="17" cm="1">
-        <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>14</v>
-      </c>
-      <c r="F236" s="17" cm="1">
-        <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.73</v>
-      </c>
-      <c r="G236" s="17" cm="1">
-        <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H236" s="17" cm="1">
-        <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.15</v>
-      </c>
-      <c r="I236" s="17" cm="1">
-        <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J236" s="17" cm="1">
-        <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K236" s="17" cm="1">
-        <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L236" s="17" cm="1">
-        <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M236" s="17" cm="1">
-        <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N236" s="17" cm="1">
-        <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O236" s="17" cm="1">
-        <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P236" s="17" cm="1">
-        <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q236" s="17" cm="1">
-        <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R236" s="17" cm="1">
-        <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S236" s="17" cm="1">
-        <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>14</v>
+        <f t="array" aca="1" ref="D236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S236" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S236" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="237" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D237" s="15" t="str" cm="1">
-        <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E237" s="17" cm="1">
-        <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>15</v>
-      </c>
-      <c r="F237" s="17" cm="1">
-        <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.74</v>
-      </c>
-      <c r="G237" s="17" cm="1">
-        <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H237" s="17" cm="1">
-        <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.17</v>
-      </c>
-      <c r="I237" s="17" cm="1">
-        <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J237" s="17" cm="1">
-        <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K237" s="17" cm="1">
-        <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L237" s="17" cm="1">
-        <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M237" s="17" cm="1">
-        <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N237" s="17" cm="1">
-        <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O237" s="17" cm="1">
-        <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P237" s="17" cm="1">
-        <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q237" s="17" cm="1">
-        <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R237" s="17" cm="1">
-        <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S237" s="17" cm="1">
-        <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>15</v>
+        <f t="array" aca="1" ref="D237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S237" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S237" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="238" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D238" s="15" t="str" cm="1">
-        <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E238" s="17" cm="1">
-        <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>16</v>
-      </c>
-      <c r="F238" s="17" cm="1">
-        <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.75</v>
-      </c>
-      <c r="G238" s="17" cm="1">
-        <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H238" s="17" cm="1">
-        <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I238" s="17" cm="1">
-        <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J238" s="17" cm="1">
-        <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K238" s="17" cm="1">
-        <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L238" s="17" cm="1">
-        <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M238" s="17" cm="1">
-        <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N238" s="17" cm="1">
-        <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O238" s="17" cm="1">
-        <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P238" s="17" cm="1">
-        <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q238" s="17" cm="1">
-        <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R238" s="17" cm="1">
-        <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S238" s="17" cm="1">
-        <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>16</v>
+        <f t="array" aca="1" ref="D238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S238" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S238" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="239" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D239" s="15" t="str" cm="1">
-        <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E239" s="17" cm="1">
-        <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>17</v>
-      </c>
-      <c r="F239" s="17" cm="1">
-        <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.76</v>
-      </c>
-      <c r="G239" s="17" cm="1">
-        <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H239" s="17" cm="1">
-        <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="I239" s="17" cm="1">
-        <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J239" s="17" cm="1">
-        <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K239" s="17" cm="1">
-        <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L239" s="17" cm="1">
-        <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M239" s="17" cm="1">
-        <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N239" s="17" cm="1">
-        <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O239" s="17" cm="1">
-        <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P239" s="17" cm="1">
-        <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q239" s="17" cm="1">
-        <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R239" s="17" cm="1">
-        <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S239" s="17" cm="1">
-        <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>17</v>
+        <f t="array" aca="1" ref="D239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S239" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S239" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="240" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D240" s="15" t="str" cm="1">
-        <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E240" s="17" cm="1">
-        <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>18</v>
-      </c>
-      <c r="F240" s="17" cm="1">
-        <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.77</v>
-      </c>
-      <c r="G240" s="17" cm="1">
-        <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H240" s="17" cm="1">
-        <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.22</v>
-      </c>
-      <c r="I240" s="17" cm="1">
-        <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J240" s="17" cm="1">
-        <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K240" s="17" cm="1">
-        <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L240" s="17" cm="1">
-        <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M240" s="17" cm="1">
-        <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N240" s="17" cm="1">
-        <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O240" s="17" cm="1">
-        <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P240" s="17" cm="1">
-        <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q240" s="17" cm="1">
-        <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R240" s="17" cm="1">
-        <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S240" s="17" cm="1">
-        <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>18</v>
+        <f t="array" aca="1" ref="D240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S240" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S240" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="241" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D241" s="15" t="str" cm="1">
-        <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E241" s="17" cm="1">
-        <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>19</v>
-      </c>
-      <c r="F241" s="17" cm="1">
-        <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.77</v>
-      </c>
-      <c r="G241" s="17" cm="1">
-        <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H241" s="17" cm="1">
-        <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.24</v>
-      </c>
-      <c r="I241" s="17" cm="1">
-        <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J241" s="17" cm="1">
-        <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K241" s="17" cm="1">
-        <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L241" s="17" cm="1">
-        <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M241" s="17" cm="1">
-        <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N241" s="17" cm="1">
-        <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O241" s="17" cm="1">
-        <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P241" s="17" cm="1">
-        <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q241" s="17" cm="1">
-        <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R241" s="17" cm="1">
-        <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S241" s="17" cm="1">
-        <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>19</v>
+        <f t="array" aca="1" ref="D241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S241" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S241" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="242" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D242" s="15" t="str" cm="1">
-        <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E242" s="17" cm="1">
-        <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>20</v>
-      </c>
-      <c r="F242" s="17" cm="1">
-        <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.78</v>
-      </c>
-      <c r="G242" s="17" cm="1">
-        <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H242" s="17" cm="1">
-        <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.26</v>
-      </c>
-      <c r="I242" s="17" cm="1">
-        <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J242" s="17" cm="1">
-        <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K242" s="17" cm="1">
-        <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L242" s="17" cm="1">
-        <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M242" s="17" cm="1">
-        <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N242" s="17" cm="1">
-        <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O242" s="17" cm="1">
-        <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P242" s="17" cm="1">
-        <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q242" s="17" cm="1">
-        <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R242" s="17" cm="1">
-        <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S242" s="17" cm="1">
-        <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>20</v>
+        <f t="array" aca="1" ref="D242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S242" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S242" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="243" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D243" s="15" t="str" cm="1">
-        <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E243" s="17" cm="1">
-        <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>21</v>
-      </c>
-      <c r="F243" s="17" cm="1">
-        <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.78</v>
-      </c>
-      <c r="G243" s="17" cm="1">
-        <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H243" s="17" cm="1">
-        <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I243" s="17" cm="1">
-        <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J243" s="17" cm="1">
-        <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K243" s="17" cm="1">
-        <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L243" s="17" cm="1">
-        <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M243" s="17" cm="1">
-        <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N243" s="17" cm="1">
-        <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O243" s="17" cm="1">
-        <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P243" s="17" cm="1">
-        <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q243" s="17" cm="1">
-        <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R243" s="17" cm="1">
-        <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S243" s="17" cm="1">
-        <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>21</v>
+        <f t="array" aca="1" ref="D243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S243" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S243" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="244" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D244" s="15" t="str" cm="1">
-        <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E244" s="17" cm="1">
-        <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>22</v>
-      </c>
-      <c r="F244" s="17" cm="1">
-        <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.78</v>
-      </c>
-      <c r="G244" s="17" cm="1">
-        <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H244" s="17" cm="1">
-        <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.31</v>
-      </c>
-      <c r="I244" s="17" cm="1">
-        <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J244" s="17" cm="1">
-        <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K244" s="17" cm="1">
-        <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L244" s="17" cm="1">
-        <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M244" s="17" cm="1">
-        <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N244" s="17" cm="1">
-        <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O244" s="17" cm="1">
-        <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P244" s="17" cm="1">
-        <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q244" s="17" cm="1">
-        <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R244" s="17" cm="1">
-        <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S244" s="17" cm="1">
-        <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>22</v>
+        <f t="array" aca="1" ref="D244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S244" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S244" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="245" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D245" s="15" t="str" cm="1">
-        <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E245" s="17" cm="1">
-        <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>23</v>
-      </c>
-      <c r="F245" s="17" cm="1">
-        <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.79</v>
-      </c>
-      <c r="G245" s="17" cm="1">
-        <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H245" s="17" cm="1">
-        <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.34</v>
-      </c>
-      <c r="I245" s="17" cm="1">
-        <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J245" s="17" cm="1">
-        <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K245" s="17" cm="1">
-        <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L245" s="17" cm="1">
-        <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M245" s="17" cm="1">
-        <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N245" s="17" cm="1">
-        <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O245" s="17" cm="1">
-        <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P245" s="17" cm="1">
-        <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q245" s="17" cm="1">
-        <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R245" s="17" cm="1">
-        <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S245" s="17" cm="1">
-        <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>23</v>
+        <f t="array" aca="1" ref="D245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S245" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S245" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="246" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D246" s="15" t="str" cm="1">
-        <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E246" s="17" cm="1">
-        <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>24</v>
-      </c>
-      <c r="F246" s="17" cm="1">
-        <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.79</v>
-      </c>
-      <c r="G246" s="17" cm="1">
-        <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H246" s="17" cm="1">
-        <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.37</v>
-      </c>
-      <c r="I246" s="17" cm="1">
-        <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J246" s="17" cm="1">
-        <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K246" s="17" cm="1">
-        <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L246" s="17" cm="1">
-        <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M246" s="17" cm="1">
-        <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N246" s="17" cm="1">
-        <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O246" s="17" cm="1">
-        <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P246" s="17" cm="1">
-        <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q246" s="17" cm="1">
-        <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R246" s="17" cm="1">
-        <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S246" s="17" cm="1">
-        <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>24</v>
+        <f t="array" aca="1" ref="D246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S246" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S246" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="247" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D247" s="15" t="str" cm="1">
-        <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Temperate</v>
-      </c>
-      <c r="E247" s="17" cm="1">
-        <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>25</v>
-      </c>
-      <c r="F247" s="17" cm="1">
-        <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.79</v>
-      </c>
-      <c r="G247" s="17" cm="1">
-        <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H247" s="17" cm="1">
-        <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.41</v>
-      </c>
-      <c r="I247" s="17" cm="1">
-        <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="J247" s="17" cm="1">
-        <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="K247" s="17" cm="1">
-        <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L247" s="17" cm="1">
-        <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M247" s="17" cm="1">
-        <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N247" s="17" cm="1">
-        <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O247" s="17" cm="1">
-        <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P247" s="17" cm="1">
-        <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q247" s="17" cm="1">
-        <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R247" s="17" cm="1">
-        <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S247" s="17" cm="1">
-        <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>25</v>
+        <f t="array" aca="1" ref="D247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S247" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S247" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="248" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D248" s="15" t="str" cm="1">
-        <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Warm</v>
-      </c>
-      <c r="E248" s="17" cm="1">
-        <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>26</v>
-      </c>
-      <c r="F248" s="17" cm="1">
-        <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.79</v>
-      </c>
-      <c r="G248" s="17" cm="1">
-        <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H248" s="17" cm="1">
-        <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.44</v>
-      </c>
-      <c r="I248" s="17" cm="1">
-        <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="J248" s="17" cm="1">
-        <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K248" s="17" cm="1">
-        <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L248" s="17" cm="1">
-        <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M248" s="17" cm="1">
-        <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N248" s="17" cm="1">
-        <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O248" s="17" cm="1">
-        <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P248" s="17" cm="1">
-        <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q248" s="17" cm="1">
-        <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R248" s="17" cm="1">
-        <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S248" s="17" cm="1">
-        <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>26</v>
+        <f t="array" aca="1" ref="D248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S248" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S248" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="249" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D249" s="15" t="str" cm="1">
-        <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Warm</v>
-      </c>
-      <c r="E249" s="17" cm="1">
-        <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>27</v>
-      </c>
-      <c r="F249" s="17" cm="1">
-        <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.8</v>
-      </c>
-      <c r="G249" s="17" cm="1">
-        <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H249" s="17" cm="1">
-        <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.48</v>
-      </c>
-      <c r="I249" s="17" cm="1">
-        <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="J249" s="17" cm="1">
-        <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K249" s="17" cm="1">
-        <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L249" s="17" cm="1">
-        <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M249" s="17" cm="1">
-        <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N249" s="17" cm="1">
-        <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O249" s="17" cm="1">
-        <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P249" s="17" cm="1">
-        <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q249" s="17" cm="1">
-        <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R249" s="17" cm="1">
-        <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S249" s="17" cm="1">
-        <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>27</v>
+        <f t="array" aca="1" ref="D249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S249" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S249" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="250" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D250" s="15" t="str" cm="1">
-        <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Warm</v>
+        <f t="array" aca="1" ref="D250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
       <c r="E250" s="17" t="str" cm="1">
-        <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>≥28</v>
-      </c>
-      <c r="F250" s="17" cm="1">
-        <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.8</v>
-      </c>
-      <c r="G250" s="17" cm="1">
-        <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H250" s="17" cm="1">
-        <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.5</v>
-      </c>
-      <c r="I250" s="17" cm="1">
-        <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.01</v>
-      </c>
-      <c r="J250" s="17" cm="1">
-        <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K250" s="17" cm="1">
-        <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L250" s="17" cm="1">
-        <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M250" s="17" cm="1">
-        <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N250" s="17" cm="1">
-        <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O250" s="17" cm="1">
-        <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P250" s="17" cm="1">
-        <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q250" s="17" cm="1">
-        <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R250" s="17" cm="1">
-        <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S250" s="17" cm="1">
-        <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>28</v>
+        <f t="array" aca="1" ref="E250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="F250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="H250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="I250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="J250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="K250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="L250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="M250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="N250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="O250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="P250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="Q250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="R250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S250" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="S250" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
@@ -7195,7 +7635,7 @@
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D257" s="17" t="s">
         <v>77</v>
       </c>
@@ -7203,30 +7643,319 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D258" s="17" t="str" cm="1">
-        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-      <c r="E258" s="17" cm="1">
-        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D258" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E258" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E258" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D259" s="15" t="str" cm="1">
-        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-      <c r="E259" s="17" cm="1">
-        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D259" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E259" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="E259" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D263" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D264" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D265" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E265" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F265" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D266" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E266" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F266" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D267" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E267" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F267" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D268" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E268" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F268" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D269" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E269" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F269" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D270" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E270" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F270" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D273" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D274" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E274" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F274" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D275" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E275" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F275" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D276" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E276" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F276" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D277" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E277" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F277" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D278" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E278" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F278" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D279" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E279" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F279" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D282" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D283" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E283" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F283" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D284" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E284" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F284" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D285" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E285" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F285" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D286" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E286" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F286" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D287" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E287" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F287" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D288" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E288" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F288" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D291" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D292" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E292" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F292" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D293" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E293" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F293" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D294" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E294" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F294" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D295" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E295" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F295" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D296" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E296" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F296" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D297" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="E297" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F297" s="17">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="17">
+  <tableParts count="21">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -7244,35 +7973,15 @@
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
     <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -7467,34 +8176,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C6F40-9188-4CB0-AF00-56A1D1AE2E37}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7511,4 +8217,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11A2AC3-1ADA-41F8-AB99-DE5FD8AAAF20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F9B851-3A8E-4BE9-8FD0-9CF81F575938}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB3165D-9942-4FD4-A356-0CB3EECA2EBA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>